--- a/data/intermediate/igae.xlsx
+++ b/data/intermediate/igae.xlsx
@@ -31,21 +31,21 @@
     <t>Var. Anual</t>
   </si>
   <si>
+    <t>Var. Mensual</t>
+  </si>
+  <si>
     <t>Índice</t>
   </si>
   <si>
-    <t>Var. Mensual</t>
-  </si>
-  <si>
     <t>737221</t>
   </si>
   <si>
+    <t>737220</t>
+  </si>
+  <si>
     <t>737219</t>
   </si>
   <si>
-    <t>737220</t>
-  </si>
-  <si>
     <t>1994/01</t>
   </si>
   <si>
@@ -1216,40 +1216,40 @@
     <t>2026/06</t>
   </si>
   <si>
+    <t>1993/02</t>
+  </si>
+  <si>
+    <t>1993/03</t>
+  </si>
+  <si>
+    <t>1993/04</t>
+  </si>
+  <si>
+    <t>1993/05</t>
+  </si>
+  <si>
+    <t>1993/06</t>
+  </si>
+  <si>
+    <t>1993/07</t>
+  </si>
+  <si>
+    <t>1993/08</t>
+  </si>
+  <si>
+    <t>1993/09</t>
+  </si>
+  <si>
+    <t>1993/10</t>
+  </si>
+  <si>
+    <t>1993/11</t>
+  </si>
+  <si>
+    <t>1993/12</t>
+  </si>
+  <si>
     <t>1993/01</t>
-  </si>
-  <si>
-    <t>1993/02</t>
-  </si>
-  <si>
-    <t>1993/03</t>
-  </si>
-  <si>
-    <t>1993/04</t>
-  </si>
-  <si>
-    <t>1993/05</t>
-  </si>
-  <si>
-    <t>1993/06</t>
-  </si>
-  <si>
-    <t>1993/07</t>
-  </si>
-  <si>
-    <t>1993/08</t>
-  </si>
-  <si>
-    <t>1993/09</t>
-  </si>
-  <si>
-    <t>1993/10</t>
-  </si>
-  <si>
-    <t>1993/11</t>
-  </si>
-  <si>
-    <t>1993/12</t>
   </si>
 </sst>
 </file>
@@ -7069,7 +7069,7 @@
         <v>400</v>
       </c>
       <c r="D392">
-        <v>56.2778528191742</v>
+        <v>2.53094689127942</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7083,7 +7083,7 @@
         <v>401</v>
       </c>
       <c r="D393">
-        <v>57.7022153855799</v>
+        <v>0.19002275222193</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7097,7 +7097,7 @@
         <v>402</v>
       </c>
       <c r="D394">
-        <v>57.8118627233486</v>
+        <v>-1.08698892937487</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7111,7 +7111,7 @@
         <v>403</v>
       </c>
       <c r="D395">
-        <v>57.1834541756804</v>
+        <v>1.21488838719286</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7125,7 +7125,7 @@
         <v>404</v>
       </c>
       <c r="D396">
-        <v>57.8781693198565</v>
+        <v>-0.757029604935477</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7139,7 +7139,7 @@
         <v>405</v>
       </c>
       <c r="D397">
-        <v>57.4400144433105</v>
+        <v>1.51307500924125</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7153,7 +7153,7 @@
         <v>406</v>
       </c>
       <c r="D398">
-        <v>58.3091249471568</v>
+        <v>-0.383129663069814</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7167,7 +7167,7 @@
         <v>407</v>
       </c>
       <c r="D399">
-        <v>58.0857253932078</v>
+        <v>-0.425961080502124</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7181,7 +7181,7 @@
         <v>408</v>
       </c>
       <c r="D400">
-        <v>57.8383028097054</v>
+        <v>-0.147602148384218</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7195,7 +7195,7 @@
         <v>409</v>
       </c>
       <c r="D401">
-        <v>57.7529322321693</v>
+        <v>-0.246182545801388</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7209,7 +7209,7 @@
         <v>410</v>
       </c>
       <c r="D402">
-        <v>57.6107545933252</v>
+        <v>1.51048424248243</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7220,10 +7220,10 @@
         <v>8</v>
       </c>
       <c r="C403" t="s">
-        <v>411</v>
+        <v>10</v>
       </c>
       <c r="D403">
-        <v>58.4809559634326</v>
+        <v>0.443921507457445</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7234,10 +7234,10 @@
         <v>8</v>
       </c>
       <c r="C404" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D404">
-        <v>58.740565504721</v>
+        <v>-0.0540930616349744</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7248,10 +7248,10 @@
         <v>8</v>
       </c>
       <c r="C405" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D405">
-        <v>58.7087909344178</v>
+        <v>0.821981539894723</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7262,10 +7262,10 @@
         <v>8</v>
       </c>
       <c r="C406" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D406">
-        <v>59.1913663581941</v>
+        <v>2.07027841107363</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7276,10 +7276,10 @@
         <v>8</v>
       </c>
       <c r="C407" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D407">
-        <v>60.4167924371273</v>
+        <v>-0.120586173711745</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7290,10 +7290,10 @@
         <v>8</v>
       </c>
       <c r="C408" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D408">
-        <v>60.343938138848</v>
+        <v>0.136582775118277</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7304,10 +7304,10 @@
         <v>8</v>
       </c>
       <c r="C409" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D409">
-        <v>60.4263575641737</v>
+        <v>-0.801470305041418</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7318,10 +7318,10 @@
         <v>8</v>
       </c>
       <c r="C410" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D410">
-        <v>59.9420582518787</v>
+        <v>0.8501986066621779</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7332,10 +7332,10 @@
         <v>8</v>
       </c>
       <c r="C411" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D411">
-        <v>60.4516847959408</v>
+        <v>0.700612252016408</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7346,10 +7346,10 @@
         <v>8</v>
       </c>
       <c r="C412" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D412">
-        <v>60.8752167061715</v>
+        <v>0.345851090951355</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7360,10 +7360,10 @@
         <v>8</v>
       </c>
       <c r="C413" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D413">
-        <v>61.0857543072688</v>
+        <v>0.36985199048809</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7374,10 +7374,10 @@
         <v>8</v>
       </c>
       <c r="C414" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D414">
-        <v>61.3116811854789</v>
+        <v>-0.863394507473358</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7388,10 +7388,10 @@
         <v>8</v>
       </c>
       <c r="C415" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D415">
-        <v>60.7823194976839</v>
+        <v>0.199014030411448</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7402,10 +7402,10 @@
         <v>8</v>
       </c>
       <c r="C416" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D416">
-        <v>60.9032848414938</v>
+        <v>-6.41657570082118</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7416,10 +7416,10 @@
         <v>8</v>
       </c>
       <c r="C417" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D417">
-        <v>56.9953794653526</v>
+        <v>-0.487545236307307</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7430,10 +7430,10 @@
         <v>8</v>
       </c>
       <c r="C418" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D418">
-        <v>56.717501207854</v>
+        <v>-2.84520769312689</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7444,10 +7444,10 @@
         <v>8</v>
       </c>
       <c r="C419" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D419">
-        <v>55.1037705001388</v>
+        <v>-0.747534777167125</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7458,10 +7458,10 @@
         <v>8</v>
       </c>
       <c r="C420" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D420">
-        <v>54.6918506521199</v>
+        <v>1.11153272839475</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7472,10 +7472,10 @@
         <v>8</v>
       </c>
       <c r="C421" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D421">
-        <v>55.299768471883</v>
+        <v>0.718944024399404</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7486,10 +7486,10 @@
         <v>8</v>
       </c>
       <c r="C422" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D422">
-        <v>55.6973428528183</v>
+        <v>0.7724314799334</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7500,10 +7500,10 @@
         <v>8</v>
       </c>
       <c r="C423" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D423">
-        <v>56.1275666624999</v>
+        <v>0.8680253561186509</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7514,10 +7514,10 @@
         <v>8</v>
       </c>
       <c r="C424" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D424">
-        <v>56.6147681729028</v>
+        <v>-2.16042856197637</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7528,10 +7528,10 @@
         <v>8</v>
       </c>
       <c r="C425" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D425">
-        <v>55.3916465509987</v>
+        <v>3.1996443816434</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7542,10 +7542,10 @@
         <v>8</v>
       </c>
       <c r="C426" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D426">
-        <v>57.1639822577675</v>
+        <v>3.58138611518464</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7556,10 +7556,10 @@
         <v>8</v>
       </c>
       <c r="C427" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D427">
-        <v>59.2112451812338</v>
+        <v>-0.127338791715359</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7570,10 +7570,10 @@
         <v>8</v>
       </c>
       <c r="C428" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D428">
-        <v>59.1358462970604</v>
+        <v>-0.882764191696606</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7584,10 +7584,10 @@
         <v>8</v>
       </c>
       <c r="C429" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D429">
-        <v>58.6138162214932</v>
+        <v>0.859296483650573</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7598,10 +7598,10 @@
         <v>8</v>
       </c>
       <c r="C430" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D430">
-        <v>59.1174826832179</v>
+        <v>-0.488401709124475</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7612,10 +7612,10 @@
         <v>8</v>
       </c>
       <c r="C431" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D431">
-        <v>58.8287518874017</v>
+        <v>1.34504671716764</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7626,10 +7626,10 @@
         <v>8</v>
       </c>
       <c r="C432" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D432">
-        <v>59.6200260834139</v>
+        <v>0.84112475694087</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="C433" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D433">
-        <v>60.1215048828961</v>
+        <v>0.0508216560550334</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7654,10 +7654,10 @@
         <v>8</v>
       </c>
       <c r="C434" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D434">
-        <v>60.1520596273228</v>
+        <v>0.0368806808984434</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7668,10 +7668,10 @@
         <v>8</v>
       </c>
       <c r="C435" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D435">
-        <v>60.1742441164878</v>
+        <v>0.780498148543285</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7682,10 +7682,10 @@
         <v>8</v>
       </c>
       <c r="C436" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D436">
-        <v>60.6439029777169</v>
+        <v>0.809934014103919</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7696,10 +7696,10 @@
         <v>8</v>
       </c>
       <c r="C437" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D437">
-        <v>61.1350785754136</v>
+        <v>1.28395285360487</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7710,10 +7710,10 @@
         <v>8</v>
       </c>
       <c r="C438" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D438">
-        <v>61.9200241613362</v>
+        <v>0.679515481429394</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7724,10 +7724,10 @@
         <v>8</v>
       </c>
       <c r="C439" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D439">
-        <v>62.3407803116173</v>
+        <v>-0.522854190395916</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7738,10 +7738,10 @@
         <v>8</v>
       </c>
       <c r="C440" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D440">
-        <v>62.0148289294325</v>
+        <v>0.396025310901638</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7752,10 +7752,10 @@
         <v>8</v>
       </c>
       <c r="C441" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D441">
-        <v>62.2604233485054</v>
+        <v>0.59041483275093</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7766,10 +7766,10 @@
         <v>8</v>
       </c>
       <c r="C442" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D442">
-        <v>62.6280181228885</v>
+        <v>1.07017920144283</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7780,10 +7780,10 @@
         <v>8</v>
       </c>
       <c r="C443" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D443">
-        <v>63.2982501471155</v>
+        <v>0.9746307341107709</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7794,10 +7794,10 @@
         <v>8</v>
       </c>
       <c r="C444" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D444">
-        <v>63.9151743472036</v>
+        <v>1.05161746950597</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7808,10 +7808,10 @@
         <v>8</v>
       </c>
       <c r="C445" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D445">
-        <v>64.587317486304</v>
+        <v>-0.020540643098732</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7822,10 +7822,10 @@
         <v>8</v>
       </c>
       <c r="C446" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D446">
-        <v>64.5740508359321</v>
+        <v>0.815585776316596</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7836,10 +7836,10 @@
         <v>8</v>
       </c>
       <c r="C447" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D447">
-        <v>65.10070760974141</v>
+        <v>0.510619492536146</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7850,10 +7850,10 @@
         <v>8</v>
       </c>
       <c r="C448" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D448">
-        <v>65.4331245125757</v>
+        <v>1.42086610161176</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7864,10 +7864,10 @@
         <v>8</v>
       </c>
       <c r="C449" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D449">
-        <v>66.3628415980003</v>
+        <v>0.899090192482155</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7878,10 +7878,10 @@
         <v>8</v>
       </c>
       <c r="C450" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D450">
-        <v>66.9595033982604</v>
+        <v>-0.319373354502583</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7892,10 +7892,10 @@
         <v>8</v>
       </c>
       <c r="C451" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D451">
-        <v>66.7456525860991</v>
+        <v>0.647424248228567</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7906,10 +7906,10 @@
         <v>8</v>
       </c>
       <c r="C452" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D452">
-        <v>67.1777801255799</v>
+        <v>1.27880525083828</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7920,10 +7920,10 @@
         <v>8</v>
       </c>
       <c r="C453" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D453">
-        <v>68.03685310522241</v>
+        <v>0.823238215993127</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7934,10 +7934,10 @@
         <v>8</v>
       </c>
       <c r="C454" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D454">
-        <v>68.5969584809437</v>
+        <v>-0.00654804318145352</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7948,10 +7948,10 @@
         <v>8</v>
       </c>
       <c r="C455" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D455">
-        <v>68.59246672248121</v>
+        <v>-0.133427115099227</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7962,10 +7962,10 @@
         <v>8</v>
       </c>
       <c r="C456" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D456">
-        <v>68.500945772958</v>
+        <v>-0.508565339857736</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7976,10 +7976,10 @@
         <v>8</v>
       </c>
       <c r="C457" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D457">
-        <v>68.15257370528199</v>
+        <v>0.696973759778197</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7990,10 +7990,10 @@
         <v>8</v>
       </c>
       <c r="C458" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D458">
-        <v>68.6275792606213</v>
+        <v>0.39013934657568</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8004,10 +8004,10 @@
         <v>8</v>
       </c>
       <c r="C459" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D459">
-        <v>68.89532244991941</v>
+        <v>-0.412047380414771</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8018,10 +8018,10 @@
         <v>8</v>
       </c>
       <c r="C460" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D460">
-        <v>68.6114410785362</v>
+        <v>-0.12633513228002</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8032,10 +8032,10 @@
         <v>8</v>
       </c>
       <c r="C461" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D461">
-        <v>68.52476072369041</v>
+        <v>0.181581639670525</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8046,10 +8046,10 @@
         <v>8</v>
       </c>
       <c r="C462" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D462">
-        <v>68.64918910779279</v>
+        <v>0.545080870952108</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8060,10 +8060,10 @@
         <v>8</v>
       </c>
       <c r="C463" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D463">
-        <v>69.0233827056831</v>
+        <v>0.749080180263917</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8074,10 +8074,10 @@
         <v>8</v>
       </c>
       <c r="C464" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D464">
-        <v>69.5404231852791</v>
+        <v>-0.139111828016136</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8088,10 +8088,10 @@
         <v>8</v>
       </c>
       <c r="C465" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D465">
-        <v>69.4436842313759</v>
+        <v>0.340507508033627</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8102,10 +8102,10 @@
         <v>8</v>
       </c>
       <c r="C466" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D466">
-        <v>69.6801451900389</v>
+        <v>0.226785481006986</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8116,10 +8116,10 @@
         <v>8</v>
       </c>
       <c r="C467" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D467">
-        <v>69.8381696424745</v>
+        <v>0.387052070042371</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8130,10 +8130,10 @@
         <v>8</v>
       </c>
       <c r="C468" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D468">
-        <v>70.10847972375539</v>
+        <v>-0.432126486948825</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8144,10 +8144,10 @@
         <v>8</v>
       </c>
       <c r="C469" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D469">
-        <v>69.8055224132719</v>
+        <v>0.776100043415617</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8158,10 +8158,10 @@
         <v>8</v>
       </c>
       <c r="C470" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D470">
-        <v>70.34728310302781</v>
+        <v>-0.13065170893678</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8172,10 +8172,10 @@
         <v>8</v>
       </c>
       <c r="C471" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D471">
-        <v>70.25537317546311</v>
+        <v>0.942425891683873</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8186,10 +8186,10 @@
         <v>8</v>
       </c>
       <c r="C472" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D472">
-        <v>70.9174780025678</v>
+        <v>-0.146426323042448</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8200,10 +8200,10 @@
         <v>8</v>
       </c>
       <c r="C473" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D473">
-        <v>70.8136361471342</v>
+        <v>0.264661329963878</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8214,10 +8214,10 @@
         <v>8</v>
       </c>
       <c r="C474" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D474">
-        <v>71.00105245835699</v>
+        <v>0.937254445636992</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8228,10 +8228,10 @@
         <v>8</v>
       </c>
       <c r="C475" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D475">
-        <v>71.66651297897199</v>
+        <v>2.74734105430052</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8242,10 +8242,10 @@
         <v>8</v>
       </c>
       <c r="C476" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D476">
-        <v>73.63543651222891</v>
+        <v>-0.613676711328603</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8256,10 +8256,10 @@
         <v>8</v>
       </c>
       <c r="C477" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D477">
-        <v>73.1835529870682</v>
+        <v>-0.117439265239538</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8270,10 +8270,10 @@
         <v>8</v>
       </c>
       <c r="C478" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D478">
-        <v>73.097606760164</v>
+        <v>0.199908982273334</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8284,10 +8284,10 @@
         <v>8</v>
       </c>
       <c r="C479" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D479">
-        <v>73.24373544190441</v>
+        <v>0.764371930675578</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8298,10 +8298,10 @@
         <v>8</v>
       </c>
       <c r="C480" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D480">
-        <v>73.80358999660061</v>
+        <v>0.739145311811273</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8312,10 +8312,10 @@
         <v>8</v>
       </c>
       <c r="C481" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D481">
-        <v>74.3491057720089</v>
+        <v>0.5578594659964911</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8326,10 +8326,10 @@
         <v>8</v>
       </c>
       <c r="C482" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D482">
-        <v>74.7638692964418</v>
+        <v>-0.5541969596076221</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8340,10 +8340,10 @@
         <v>8</v>
       </c>
       <c r="C483" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D483">
-        <v>74.3495302059159</v>
+        <v>-0.0203502710159675</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8354,10 +8354,10 @@
         <v>8</v>
       </c>
       <c r="C484" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D484">
-        <v>74.3343998750199</v>
+        <v>0.100605256545738</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8368,10 +8368,10 @@
         <v>8</v>
       </c>
       <c r="C485" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D485">
-        <v>74.4091841887159</v>
+        <v>-0.317558334113321</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8382,10 +8382,10 @@
         <v>8</v>
       </c>
       <c r="C486" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D486">
-        <v>74.1728916229789</v>
+        <v>-0.9133467291890131</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8396,10 +8396,10 @@
         <v>8</v>
       </c>
       <c r="C487" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D487">
-        <v>73.49543594339551</v>
+        <v>0.929402111921851</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8410,10 +8410,10 @@
         <v>8</v>
       </c>
       <c r="C488" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D488">
-        <v>74.1785040772196</v>
+        <v>-0.813318884051717</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8424,10 +8424,10 @@
         <v>8</v>
       </c>
       <c r="C489" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D489">
-        <v>73.5751962956525</v>
+        <v>-0.200771384870413</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8438,10 +8438,10 @@
         <v>8</v>
       </c>
       <c r="C490" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D490">
-        <v>73.4274783551286</v>
+        <v>-0.216454180735726</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8452,10 +8452,10 @@
         <v>8</v>
       </c>
       <c r="C491" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D491">
-        <v>73.2685415084201</v>
+        <v>-0.128052902384201</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8466,10 +8466,10 @@
         <v>8</v>
       </c>
       <c r="C492" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D492">
-        <v>73.174719014484</v>
+        <v>0.09342337018944941</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8480,10 +8480,10 @@
         <v>8</v>
       </c>
       <c r="C493" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D493">
-        <v>73.243081303114</v>
+        <v>-0.169680963476093</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8494,10 +8494,10 @@
         <v>8</v>
       </c>
       <c r="C494" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D494">
-        <v>73.11880173707929</v>
+        <v>0.52618627742651</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8508,10 +8508,10 @@
         <v>8</v>
       </c>
       <c r="C495" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D495">
-        <v>73.5035428380385</v>
+        <v>-0.127108644691543</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8522,10 +8522,10 @@
         <v>8</v>
       </c>
       <c r="C496" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D496">
-        <v>73.4101134809368</v>
+        <v>-1.12400670904435</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8536,10 +8536,10 @@
         <v>8</v>
       </c>
       <c r="C497" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D497">
-        <v>72.584978880294</v>
+        <v>0.396137551714659</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8550,10 +8550,10 @@
         <v>8</v>
       </c>
       <c r="C498" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D498">
-        <v>72.872515238543</v>
+        <v>-0.221202511296659</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8564,10 +8564,10 @@
         <v>8</v>
       </c>
       <c r="C499" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D499">
-        <v>72.7113194047903</v>
+        <v>-1.20863640065264</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8578,10 +8578,10 @@
         <v>8</v>
       </c>
       <c r="C500" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D500">
-        <v>71.8325039310692</v>
+        <v>-0.105053147262013</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8592,10 +8592,10 @@
         <v>8</v>
       </c>
       <c r="C501" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D501">
-        <v>71.7570416249325</v>
+        <v>0.84170185747825</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8606,10 +8606,10 @@
         <v>8</v>
       </c>
       <c r="C502" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D502">
-        <v>72.361021977161</v>
+        <v>0.779846659878713</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8620,10 +8620,10 @@
         <v>8</v>
       </c>
       <c r="C503" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D503">
-        <v>72.925326990104</v>
+        <v>0.0599001663699639</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8634,10 +8634,10 @@
         <v>8</v>
       </c>
       <c r="C504" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D504">
-        <v>72.9690093822969</v>
+        <v>-0.07921391473217911</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8648,10 +8648,10 @@
         <v>8</v>
       </c>
       <c r="C505" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D505">
-        <v>72.9112077734239</v>
+        <v>0.392631990984449</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8662,10 +8662,10 @@
         <v>8</v>
       </c>
       <c r="C506" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D506">
-        <v>73.19748050015551</v>
+        <v>0.812807510240776</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8676,10 +8676,10 @@
         <v>8</v>
       </c>
       <c r="C507" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D507">
-        <v>73.7924351189678</v>
+        <v>-0.248639901277825</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8690,10 +8690,10 @@
         <v>8</v>
       </c>
       <c r="C508" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D508">
-        <v>73.6089576811375</v>
+        <v>0.480842598246167</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8704,10 +8704,10 @@
         <v>8</v>
       </c>
       <c r="C509" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D509">
-        <v>73.9629009057934</v>
+        <v>-0.603282281516837</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8718,10 +8718,10 @@
         <v>8</v>
       </c>
       <c r="C510" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D510">
-        <v>73.5166958297329</v>
+        <v>0.0635157909927742</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8732,10 +8732,10 @@
         <v>8</v>
       </c>
       <c r="C511" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D511">
-        <v>73.56339054060091</v>
+        <v>-0.0688990060224826</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8746,10 +8746,10 @@
         <v>8</v>
       </c>
       <c r="C512" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D512">
-        <v>73.512706095722</v>
+        <v>0.600218228527827</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8760,10 +8760,10 @@
         <v>8</v>
       </c>
       <c r="C513" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D513">
-        <v>73.95394275799261</v>
+        <v>-0.732784647150719</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8774,10 +8774,10 @@
         <v>8</v>
       </c>
       <c r="C514" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D514">
-        <v>73.4120196194994</v>
+        <v>0.125454820641702</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8788,10 +8788,10 @@
         <v>8</v>
       </c>
       <c r="C515" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D515">
-        <v>73.5041185370425</v>
+        <v>-0.290943270868882</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8802,10 +8802,10 @@
         <v>8</v>
       </c>
       <c r="C516" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D516">
-        <v>73.29026325034749</v>
+        <v>0.82511026937202</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8816,10 +8816,10 @@
         <v>8</v>
       </c>
       <c r="C517" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D517">
-        <v>73.8949887388759</v>
+        <v>0.0304788625566932</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8830,10 +8830,10 @@
         <v>8</v>
       </c>
       <c r="C518" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D518">
-        <v>73.91751109092991</v>
+        <v>-0.9255983893269319</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8844,10 +8844,10 @@
         <v>8</v>
       </c>
       <c r="C519" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D519">
-        <v>73.2333317988417</v>
+        <v>0.306598409473491</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8858,10 +8858,10 @@
         <v>8</v>
       </c>
       <c r="C520" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D520">
-        <v>73.45786402934139</v>
+        <v>0.397071579818054</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8872,10 +8872,10 @@
         <v>8</v>
       </c>
       <c r="C521" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D521">
-        <v>73.7495443305433</v>
+        <v>0.1854858294424</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8886,10 +8886,10 @@
         <v>8</v>
       </c>
       <c r="C522" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D522">
-        <v>73.88633928455479</v>
+        <v>1.20845001526764</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8900,10 +8900,10 @@
         <v>8</v>
       </c>
       <c r="C523" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D523">
-        <v>74.7792187629197</v>
+        <v>0.469265924567419</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8914,10 +8914,10 @@
         <v>8</v>
       </c>
       <c r="C524" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D524">
-        <v>75.13013215523181</v>
+        <v>0.298635993325846</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8928,10 +8928,10 @@
         <v>8</v>
       </c>
       <c r="C525" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D525">
-        <v>75.3544977716806</v>
+        <v>1.22950754167084</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8942,10 +8942,10 @@
         <v>8</v>
       </c>
       <c r="C526" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D526">
-        <v>76.2809870047716</v>
+        <v>-0.340993000436451</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8956,10 +8956,10 @@
         <v>8</v>
       </c>
       <c r="C527" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D527">
-        <v>76.02087417842149</v>
+        <v>0.166931279644822</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8970,10 +8970,10 @@
         <v>8</v>
       </c>
       <c r="C528" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D528">
-        <v>76.14777679648471</v>
+        <v>0.470757081735118</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8984,10 +8984,10 @@
         <v>8</v>
       </c>
       <c r="C529" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D529">
-        <v>76.50624784833801</v>
+        <v>-0.602405487237634</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8998,10 +8998,10 @@
         <v>8</v>
       </c>
       <c r="C530" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D530">
-        <v>76.04537001321999</v>
+        <v>0.250312742589198</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9012,10 +9012,10 @@
         <v>8</v>
       </c>
       <c r="C531" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D531">
-        <v>76.23572126451219</v>
+        <v>-0.0143458358501602</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9026,10 +9026,10 @@
         <v>8</v>
       </c>
       <c r="C532" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D532">
-        <v>76.2247846130804</v>
+        <v>0.299716668434113</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9040,10 +9040,10 @@
         <v>8</v>
       </c>
       <c r="C533" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D533">
-        <v>76.45324299804381</v>
+        <v>0.892949767491968</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9054,10 +9054,10 @@
         <v>8</v>
       </c>
       <c r="C534" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D534">
-        <v>77.1359320536349</v>
+        <v>-0.0879711574043318</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9068,10 +9068,10 @@
         <v>8</v>
       </c>
       <c r="C535" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D535">
-        <v>77.06807468143271</v>
+        <v>0.0860295867195937</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9082,10 +9082,10 @@
         <v>8</v>
       </c>
       <c r="C536" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D536">
-        <v>77.13437602757389</v>
+        <v>0.178411087304853</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9096,10 +9096,10 @@
         <v>8</v>
       </c>
       <c r="C537" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D537">
-        <v>77.27199230653051</v>
+        <v>-0.435536805186476</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9110,10 +9110,10 @@
         <v>8</v>
       </c>
       <c r="C538" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D538">
-        <v>76.9354443399347</v>
+        <v>0.51543440881352</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9124,10 +9124,10 @@
         <v>8</v>
       </c>
       <c r="C539" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D539">
-        <v>77.3319960926363</v>
+        <v>0.234062631258181</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9138,10 +9138,10 @@
         <v>8</v>
       </c>
       <c r="C540" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D540">
-        <v>77.5130013974952</v>
+        <v>-0.840883981317309</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9152,10 +9152,10 @@
         <v>8</v>
       </c>
       <c r="C541" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D541">
-        <v>76.8612069853054</v>
+        <v>0.32812594517897</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9166,10 +9166,10 @@
         <v>8</v>
       </c>
       <c r="C542" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D542">
-        <v>77.1134085472019</v>
+        <v>1.3083630258572</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9180,10 +9180,10 @@
         <v>8</v>
       </c>
       <c r="C543" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D543">
-        <v>78.1223318726117</v>
+        <v>0.529317674483898</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9194,10 +9194,10 @@
         <v>8</v>
       </c>
       <c r="C544" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D544">
-        <v>78.5358471829324</v>
+        <v>0.284830019384597</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9208,10 +9208,10 @@
         <v>8</v>
       </c>
       <c r="C545" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D545">
-        <v>78.7595408516874</v>
+        <v>0.911525854451201</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9222,10 +9222,10 @@
         <v>8</v>
       </c>
       <c r="C546" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D546">
-        <v>79.4774544293976</v>
+        <v>0.616198357793718</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9236,10 +9236,10 @@
         <v>8</v>
       </c>
       <c r="C547" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D547">
-        <v>79.9671931984078</v>
+        <v>1.86014889426058</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9250,10 +9250,10 @@
         <v>8</v>
       </c>
       <c r="C548" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D548">
-        <v>81.4547020584592</v>
+        <v>-1.04805648583555</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9264,10 +9264,10 @@
         <v>8</v>
       </c>
       <c r="C549" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D549">
-        <v>80.6010107705175</v>
+        <v>0.101828487623146</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9278,10 +9278,10 @@
         <v>8</v>
       </c>
       <c r="C550" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D550">
-        <v>80.6830855607941</v>
+        <v>0.544531861750963</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9292,10 +9292,10 @@
         <v>8</v>
       </c>
       <c r="C551" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D551">
-        <v>81.1224306687164</v>
+        <v>1.02665251227829</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9306,10 +9306,10 @@
         <v>8</v>
       </c>
       <c r="C552" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D552">
-        <v>81.955276141198</v>
+        <v>-0.146184077310518</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9320,10 +9320,10 @@
         <v>8</v>
       </c>
       <c r="C553" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D553">
-        <v>81.8354705769637</v>
+        <v>-0.0468065134788698</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9334,10 +9334,10 @@
         <v>8</v>
       </c>
       <c r="C554" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D554">
-        <v>81.79716624639759</v>
+        <v>0.254417671761553</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9348,10 +9348,10 @@
         <v>8</v>
       </c>
       <c r="C555" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D555">
-        <v>82.0052726923286</v>
+        <v>-0.036785074157708</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9362,10 +9362,10 @@
         <v>8</v>
       </c>
       <c r="C556" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D556">
-        <v>81.9751069919555</v>
+        <v>0.285075229037424</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9376,10 +9376,10 @@
         <v>8</v>
       </c>
       <c r="C557" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D557">
-        <v>82.2087977159665</v>
+        <v>-0.326998499714082</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9390,10 +9390,10 @@
         <v>8</v>
       </c>
       <c r="C558" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D558">
-        <v>81.9399761808023</v>
+        <v>0.460270705516197</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9404,10 +9404,10 @@
         <v>8</v>
       </c>
       <c r="C559" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D559">
-        <v>82.31712188726949</v>
+        <v>0.0887322661855539</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9418,10 +9418,10 @@
         <v>8</v>
       </c>
       <c r="C560" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D560">
-        <v>82.3901637349788</v>
+        <v>0.0657334942389509</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9432,10 +9432,10 @@
         <v>8</v>
       </c>
       <c r="C561" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D561">
-        <v>82.44432166851099</v>
+        <v>0.567817349531907</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9446,10 +9446,10 @@
         <v>8</v>
       </c>
       <c r="C562" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D562">
-        <v>82.9124548306487</v>
+        <v>0.455760830752916</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9460,10 +9460,10 @@
         <v>8</v>
       </c>
       <c r="C563" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D563">
-        <v>83.29033732358251</v>
+        <v>0.217287599396543</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9474,10 +9474,10 @@
         <v>8</v>
       </c>
       <c r="C564" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D564">
-        <v>83.47131689808219</v>
+        <v>0.418336338873471</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9488,10 +9488,10 @@
         <v>8</v>
       </c>
       <c r="C565" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D565">
-        <v>83.8205077492031</v>
+        <v>-0.17170109464969</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9502,10 +9502,10 @@
         <v>8</v>
       </c>
       <c r="C566" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D566">
-        <v>83.6765870198568</v>
+        <v>0.231348331861647</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9516,10 +9516,10 @@
         <v>8</v>
       </c>
       <c r="C567" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D567">
-        <v>83.87017140808599</v>
+        <v>0.204720340985665</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9530,10 +9530,10 @@
         <v>8</v>
       </c>
       <c r="C568" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D568">
-        <v>84.0418707089779</v>
+        <v>-0.146338556433356</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9544,10 +9544,10 @@
         <v>8</v>
       </c>
       <c r="C569" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D569">
-        <v>83.91888504858279</v>
+        <v>-0.380763791881411</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9558,10 +9558,10 @@
         <v>8</v>
       </c>
       <c r="C570" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D570">
-        <v>83.59935231976721</v>
+        <v>0.0502093995884634</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9572,10 +9572,10 @@
         <v>8</v>
       </c>
       <c r="C571" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D571">
-        <v>83.64132705262681</v>
+        <v>0.588761708775065</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9586,10 +9586,10 @@
         <v>8</v>
       </c>
       <c r="C572" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D572">
-        <v>84.133775159024</v>
+        <v>0.140010264029233</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9600,10 +9600,10 @@
         <v>8</v>
       </c>
       <c r="C573" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D573">
-        <v>84.2515710797619</v>
+        <v>-1.38024239977019</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9614,10 +9614,10 @@
         <v>8</v>
       </c>
       <c r="C574" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D574">
-        <v>83.08869517324651</v>
+        <v>1.92613250506852</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9628,10 +9628,10 @@
         <v>8</v>
       </c>
       <c r="C575" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D575">
-        <v>84.6890935390157</v>
+        <v>-0.5256177119950191</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9642,10 +9642,10 @@
         <v>8</v>
       </c>
       <c r="C576" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D576">
-        <v>84.2439526632466</v>
+        <v>0.798440963350644</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9656,10 +9656,10 @@
         <v>8</v>
       </c>
       <c r="C577" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D577">
-        <v>84.91659089045569</v>
+        <v>-0.07841953875055151</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9670,10 +9670,10 @@
         <v>8</v>
       </c>
       <c r="C578" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D578">
-        <v>84.8499996915567</v>
+        <v>-1.07946107072638</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9684,10 +9684,10 @@
         <v>8</v>
       </c>
       <c r="C579" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D579">
-        <v>83.9340769763749</v>
+        <v>-0.293184792976353</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9698,10 +9698,10 @@
         <v>8</v>
       </c>
       <c r="C580" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D580">
-        <v>83.6879950265551</v>
+        <v>0.101809335484093</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9712,10 +9712,10 @@
         <v>8</v>
       </c>
       <c r="C581" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D581">
-        <v>83.7731972181716</v>
+        <v>-1.35499879361984</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9726,10 +9726,10 @@
         <v>8</v>
       </c>
       <c r="C582" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D582">
-        <v>82.63807140648861</v>
+        <v>-1.12141270688347</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9740,10 +9740,10 @@
         <v>8</v>
       </c>
       <c r="C583" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D583">
-        <v>81.7113575730128</v>
+        <v>-4.35151843326913</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9754,10 +9754,10 @@
         <v>8</v>
       </c>
       <c r="C584" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D584">
-        <v>78.1556727861487</v>
+        <v>-0.386771061845903</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9768,10 +9768,10 @@
         <v>8</v>
       </c>
       <c r="C585" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D585">
-        <v>77.8533892606209</v>
+        <v>-0.244403007911242</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9782,10 +9782,10 @@
         <v>8</v>
       </c>
       <c r="C586" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D586">
-        <v>77.6631132355071</v>
+        <v>-0.869779051318886</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9796,10 +9796,10 @@
         <v>8</v>
       </c>
       <c r="C587" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D587">
-        <v>76.98761574598259</v>
+        <v>-0.467658568850249</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9810,10 +9810,10 @@
         <v>8</v>
       </c>
       <c r="C588" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D588">
-        <v>76.627576563993</v>
+        <v>1.58583577383644</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9824,10 +9824,10 @@
         <v>8</v>
       </c>
       <c r="C589" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D589">
-        <v>77.84276408576871</v>
+        <v>1.7849667621618</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9838,10 +9838,10 @@
         <v>8</v>
       </c>
       <c r="C590" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D590">
-        <v>79.2322315514477</v>
+        <v>-0.196659511523434</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9852,10 +9852,10 @@
         <v>8</v>
       </c>
       <c r="C591" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D591">
-        <v>79.07641383190951</v>
+        <v>0.754510358712102</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9866,10 +9866,10 @@
         <v>8</v>
       </c>
       <c r="C592" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D592">
-        <v>79.6730535655693</v>
+        <v>0.772650877370951</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9880,10 +9880,10 @@
         <v>8</v>
       </c>
       <c r="C593" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D593">
-        <v>80.2886481129719</v>
+        <v>0.994767112109907</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9894,10 +9894,10 @@
         <v>8</v>
       </c>
       <c r="C594" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D594">
-        <v>81.0873331791574</v>
+        <v>0.576211780630742</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9908,10 +9908,10 @@
         <v>8</v>
       </c>
       <c r="C595" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D595">
-        <v>81.554567945535</v>
+        <v>-0.860239327838175</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9922,10 +9922,10 @@
         <v>8</v>
       </c>
       <c r="C596" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D596">
-        <v>80.853003478419</v>
+        <v>0.8169937666900881</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9936,10 +9936,10 @@
         <v>8</v>
       </c>
       <c r="C597" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D597">
-        <v>81.51356747701939</v>
+        <v>0.683370734365596</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9950,10 +9950,10 @@
         <v>8</v>
       </c>
       <c r="C598" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D598">
-        <v>82.0706073416947</v>
+        <v>1.15424957990928</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9964,10 +9964,10 @@
         <v>8</v>
       </c>
       <c r="C599" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D599">
-        <v>83.0179069821652</v>
+        <v>-0.19851274099828</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9978,10 +9978,10 @@
         <v>8</v>
       </c>
       <c r="C600" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D600">
-        <v>82.8531058594955</v>
+        <v>-0.0280204065333023</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9992,10 +9992,10 @@
         <v>8</v>
       </c>
       <c r="C601" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D601">
-        <v>82.8298900824082</v>
+        <v>0.346715038704715</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10006,10 +10006,10 @@
         <v>8</v>
       </c>
       <c r="C602" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D602">
-        <v>83.1170737678665</v>
+        <v>0.229235069713862</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10020,10 +10020,10 @@
         <v>8</v>
       </c>
       <c r="C603" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D603">
-        <v>83.3076072498624</v>
+        <v>0.289634649307979</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10034,10 +10034,10 @@
         <v>8</v>
       </c>
       <c r="C604" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D604">
-        <v>83.5488949459674</v>
+        <v>-0.0404035925294255</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="C605" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D605">
-        <v>83.5151381908906</v>
+        <v>0.200520998794662</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10062,10 +10062,10 @@
         <v>8</v>
       </c>
       <c r="C606" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D606">
-        <v>83.68260358013571</v>
+        <v>0.814642199402615</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10076,10 +10076,10 @@
         <v>8</v>
       </c>
       <c r="C607" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D607">
-        <v>84.3643173824583</v>
+        <v>0.140127986486127</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10090,10 +10090,10 @@
         <v>8</v>
       </c>
       <c r="C608" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D608">
-        <v>84.4825354017191</v>
+        <v>0.225543706436415</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -10104,10 +10104,10 @@
         <v>8</v>
       </c>
       <c r="C609" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D609">
-        <v>84.6730804433556</v>
+        <v>0.631064297037298</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10118,10 +10118,10 @@
         <v>8</v>
       </c>
       <c r="C610" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D610">
-        <v>85.2074220232353</v>
+        <v>-0.981557964363622</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -10132,10 +10132,10 @@
         <v>8</v>
       </c>
       <c r="C611" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D611">
-        <v>84.3710617861373</v>
+        <v>1.36932795937448</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10146,10 +10146,10 @@
         <v>8</v>
       </c>
       <c r="C612" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D612">
-        <v>85.526378324796</v>
+        <v>0.40161604868707</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -10160,10 +10160,10 @@
         <v>8</v>
       </c>
       <c r="C613" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D613">
-        <v>85.8698659860092</v>
+        <v>0.303287513654471</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -10174,10 +10174,10 @@
         <v>8</v>
       </c>
       <c r="C614" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D614">
-        <v>86.1302985675366</v>
+        <v>0.826320664735558</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -10188,10 +10188,10 @@
         <v>8</v>
       </c>
       <c r="C615" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D615">
-        <v>86.84201102319859</v>
+        <v>0.120213325318219</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -10202,10 +10202,10 @@
         <v>8</v>
       </c>
       <c r="C616" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D616">
-        <v>86.9464066924228</v>
+        <v>0.0473501506260465</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -10216,10 +10216,10 @@
         <v>8</v>
       </c>
       <c r="C617" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D617">
-        <v>86.9875759469556</v>
+        <v>0.705222892720658</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -10230,10 +10230,10 @@
         <v>8</v>
       </c>
       <c r="C618" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D618">
-        <v>87.6010322463563</v>
+        <v>-0.0546249660210885</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -10244,10 +10244,10 @@
         <v>8</v>
       </c>
       <c r="C619" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D619">
-        <v>87.5531802122576</v>
+        <v>0.894545583631512</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -10258,10 +10258,10 @@
         <v>8</v>
       </c>
       <c r="C620" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D620">
-        <v>88.3363833191753</v>
+        <v>0.20546748393977</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -10272,10 +10272,10 @@
         <v>8</v>
       </c>
       <c r="C621" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D621">
-        <v>88.51788586338461</v>
+        <v>0.196228727209524</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -10286,10 +10286,10 @@
         <v>8</v>
       </c>
       <c r="C622" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D622">
-        <v>88.6915833841671</v>
+        <v>0.244924542556069</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -10300,10 +10300,10 @@
         <v>8</v>
       </c>
       <c r="C623" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D623">
-        <v>88.9088108390565</v>
+        <v>-0.443833386109749</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -10314,10 +10314,10 @@
         <v>8</v>
       </c>
       <c r="C624" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D624">
-        <v>88.5142038533596</v>
+        <v>0.67545609028592</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -10328,10 +10328,10 @@
         <v>8</v>
       </c>
       <c r="C625" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D625">
-        <v>89.11207843405521</v>
+        <v>0.404107447885727</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -10342,10 +10342,10 @@
         <v>8</v>
       </c>
       <c r="C626" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D626">
-        <v>89.472186979973</v>
+        <v>-0.572745819509257</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -10356,10 +10356,10 @@
         <v>8</v>
       </c>
       <c r="C627" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D627">
-        <v>88.9597387694217</v>
+        <v>0.399649989195328</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -10370,10 +10370,10 @@
         <v>8</v>
       </c>
       <c r="C628" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D628">
-        <v>89.3152663558019</v>
+        <v>-0.112050167662614</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -10384,10 +10384,10 @@
         <v>8</v>
       </c>
       <c r="C629" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D629">
-        <v>89.21518845010191</v>
+        <v>0.974239553041945</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -10398,10 +10398,10 @@
         <v>8</v>
       </c>
       <c r="C630" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D630">
-        <v>90.0843581033037</v>
+        <v>-0.357178349405141</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -10412,10 +10412,10 @@
         <v>8</v>
       </c>
       <c r="C631" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D631">
-        <v>89.7625962799581</v>
+        <v>-0.0870590644980629</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -10426,10 +10426,10 @@
         <v>8</v>
       </c>
       <c r="C632" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D632">
-        <v>89.6844498033676</v>
+        <v>-0.139959318950611</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -10440,10 +10440,10 @@
         <v>8</v>
       </c>
       <c r="C633" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D633">
-        <v>89.5589280582182</v>
+        <v>-0.0690991315545619</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -10454,10 +10454,10 @@
         <v>8</v>
       </c>
       <c r="C634" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D634">
-        <v>89.4970436167004</v>
+        <v>-0.335437896452007</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -10468,10 +10468,10 @@
         <v>8</v>
       </c>
       <c r="C635" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D635">
-        <v>89.1968366162058</v>
+        <v>0.818326784524204</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -10482,10 +10482,10 @@
         <v>8</v>
       </c>
       <c r="C636" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D636">
-        <v>89.9267582211845</v>
+        <v>-0.316599749079383</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -10496,10 +10496,10 @@
         <v>8</v>
       </c>
       <c r="C637" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D637">
-        <v>89.642050330301</v>
+        <v>0.0550659100655437</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -10510,10 +10510,10 @@
         <v>8</v>
       </c>
       <c r="C638" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D638">
-        <v>89.6914125411168</v>
+        <v>0.630737155343786</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -10524,10 +10524,10 @@
         <v>8</v>
       </c>
       <c r="C639" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D639">
-        <v>90.2571296051663</v>
+        <v>-0.13687408132369</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -10538,10 +10538,10 @@
         <v>8</v>
       </c>
       <c r="C640" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D640">
-        <v>90.13359098819009</v>
+        <v>0.317327436550796</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -10552,10 +10552,10 @@
         <v>8</v>
       </c>
       <c r="C641" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D641">
-        <v>90.4196096019441</v>
+        <v>-0.227972798821041</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -10566,10 +10566,10 @@
         <v>8</v>
       </c>
       <c r="C642" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D642">
-        <v>90.2134774872515</v>
+        <v>0.599471169391541</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -10580,10 +10580,10 @@
         <v>8</v>
       </c>
       <c r="C643" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D643">
-        <v>90.7542812756931</v>
+        <v>-0.814324063360461</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -10594,10 +10594,10 @@
         <v>8</v>
       </c>
       <c r="C644" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D644">
-        <v>90.0152473247353</v>
+        <v>1.3124604486813</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -10608,10 +10608,10 @@
         <v>8</v>
       </c>
       <c r="C645" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D645">
-        <v>91.19666184365509</v>
+        <v>0.281098475702413</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -10622,10 +10622,10 @@
         <v>8</v>
       </c>
       <c r="C646" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D646">
-        <v>91.4530142699891</v>
+        <v>0.457899871940048</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -10636,10 +10636,10 @@
         <v>8</v>
       </c>
       <c r="C647" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D647">
-        <v>91.8717775052167</v>
+        <v>0.736474479838356</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -10650,10 +10650,10 @@
         <v>8</v>
       </c>
       <c r="C648" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D648">
-        <v>92.5483897007165</v>
+        <v>-0.369085450739459</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -10664,10 +10664,10 @@
         <v>8</v>
       </c>
       <c r="C649" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D649">
-        <v>92.20680705943749</v>
+        <v>0.615325115394327</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -10678,10 +10678,10 @@
         <v>8</v>
       </c>
       <c r="C650" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D650">
-        <v>92.77417870137739</v>
+        <v>-0.674051381866458</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -10692,10 +10692,10 @@
         <v>8</v>
       </c>
       <c r="C651" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D651">
-        <v>92.14883306782551</v>
+        <v>0.228516240551846</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -10706,10 +10706,10 @@
         <v>8</v>
       </c>
       <c r="C652" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D652">
-        <v>92.3594081168645</v>
+        <v>0.704349559636364</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -10720,10 +10720,10 @@
         <v>8</v>
       </c>
       <c r="C653" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D653">
-        <v>93.0099412012184</v>
+        <v>0.157471192311731</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -10734,10 +10734,10 @@
         <v>8</v>
       </c>
       <c r="C654" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D654">
-        <v>93.1564050645964</v>
+        <v>-0.112778059977359</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -10748,10 +10748,10 @@
         <v>8</v>
       </c>
       <c r="C655" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D655">
-        <v>93.0513450782199</v>
+        <v>0.0712235233494951</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -10762,10 +10762,10 @@
         <v>8</v>
       </c>
       <c r="C656" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D656">
-        <v>93.1176195247087</v>
+        <v>0.380070428711932</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -10776,10 +10776,10 @@
         <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D657">
-        <v>93.4715320604426</v>
+        <v>0.210356662235345</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -10790,10 +10790,10 @@
         <v>8</v>
       </c>
       <c r="C658" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D658">
-        <v>93.6681556554252</v>
+        <v>0.899815380768088</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -10804,10 +10804,10 @@
         <v>8</v>
       </c>
       <c r="C659" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D659">
-        <v>94.5109961268945</v>
+        <v>-0.699952048570518</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -10818,10 +10818,10 @@
         <v>8</v>
       </c>
       <c r="C660" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D660">
-        <v>93.8494644733799</v>
+        <v>0.474933972681679</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -10832,10 +10832,10 @@
         <v>8</v>
       </c>
       <c r="C661" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D661">
-        <v>94.29518746334379</v>
+        <v>0.769814037456573</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -10846,10 +10846,10 @@
         <v>8</v>
       </c>
       <c r="C662" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D662">
-        <v>95.0210850530826</v>
+        <v>-0.0455187933596335</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -10860,10 +10860,10 @@
         <v>8</v>
       </c>
       <c r="C663" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D663">
-        <v>94.9778326017292</v>
+        <v>1.52971810501259</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -10874,10 +10874,10 @@
         <v>8</v>
       </c>
       <c r="C664" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D664">
-        <v>96.4307257027864</v>
+        <v>-1.23660674069079</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -10888,10 +10888,10 @@
         <v>8</v>
       </c>
       <c r="C665" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D665">
-        <v>95.2382568486487</v>
+        <v>-0.655740681079109</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -10902,10 +10902,10 @@
         <v>8</v>
       </c>
       <c r="C666" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D666">
-        <v>94.6137408545415</v>
+        <v>0.293929936020665</v>
       </c>
     </row>
     <row r="667" spans="1:4">
@@ -10916,10 +10916,10 @@
         <v>8</v>
       </c>
       <c r="C667" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D667">
-        <v>94.89183896250201</v>
+        <v>0.174309327542344</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -10930,10 +10930,10 @@
         <v>8</v>
       </c>
       <c r="C668" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D668">
-        <v>95.0572442888901</v>
+        <v>0.519283008854687</v>
       </c>
     </row>
     <row r="669" spans="1:4">
@@ -10944,10 +10944,10 @@
         <v>8</v>
       </c>
       <c r="C669" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D669">
-        <v>95.5508604071678</v>
+        <v>-0.476254609341931</v>
       </c>
     </row>
     <row r="670" spans="1:4">
@@ -10958,10 +10958,10 @@
         <v>8</v>
       </c>
       <c r="C670" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D670">
-        <v>95.0957950302128</v>
+        <v>0.09571475593792569</v>
       </c>
     </row>
     <row r="671" spans="1:4">
@@ -10972,10 +10972,10 @@
         <v>8</v>
       </c>
       <c r="C671" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D671">
-        <v>95.18681573833319</v>
+        <v>0.351944812502003</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -10986,10 +10986,10 @@
         <v>8</v>
       </c>
       <c r="C672" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D672">
-        <v>95.52182079851011</v>
+        <v>0.42281757424969</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -11000,10 +11000,10 @@
         <v>8</v>
       </c>
       <c r="C673" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D673">
-        <v>95.9257038440895</v>
+        <v>-0.09792146924234579</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -11014,10 +11014,10 @@
         <v>8</v>
       </c>
       <c r="C674" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D674">
-        <v>95.8317719855043</v>
+        <v>0.321474781878295</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -11028,10 +11028,10 @@
         <v>8</v>
       </c>
       <c r="C675" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D675">
-        <v>96.1398469654648</v>
+        <v>0.640181024426734</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -11042,10 +11042,10 @@
         <v>8</v>
       </c>
       <c r="C676" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D676">
-        <v>96.7553160226506</v>
+        <v>0.253260544759648</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -11056,10 +11056,10 @@
         <v>8</v>
       </c>
       <c r="C677" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D677">
-        <v>97.0003590630935</v>
+        <v>0.249431074226147</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -11070,10 +11070,10 @@
         <v>8</v>
       </c>
       <c r="C678" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D678">
-        <v>97.2423081007078</v>
+        <v>0.488593786335612</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -11084,10 +11084,10 @@
         <v>8</v>
       </c>
       <c r="C679" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D679">
-        <v>97.7174279757772</v>
+        <v>0.296002383113381</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -11098,10 +11098,10 @@
         <v>8</v>
       </c>
       <c r="C680" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D680">
-        <v>98.0066738913026</v>
+        <v>-0.469880364631536</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -11112,10 +11112,10 @@
         <v>8</v>
       </c>
       <c r="C681" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D681">
-        <v>97.5461597746589</v>
+        <v>0.335895730078462</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -11126,10 +11126,10 @@
         <v>8</v>
       </c>
       <c r="C682" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D682">
-        <v>97.8738131601975</v>
+        <v>-0.0256172209270766</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -11140,10 +11140,10 @@
         <v>8</v>
       </c>
       <c r="C683" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D683">
-        <v>97.8487406092505</v>
+        <v>-0.205127418374373</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -11154,10 +11154,10 @@
         <v>8</v>
       </c>
       <c r="C684" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D684">
-        <v>97.64802601372691</v>
+        <v>0.5198770785638021</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -11168,10 +11168,10 @@
         <v>8</v>
       </c>
       <c r="C685" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D685">
-        <v>98.1556757186423</v>
+        <v>-0.8778971811228</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -11182,10 +11182,10 @@
         <v>8</v>
       </c>
       <c r="C686" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D686">
-        <v>97.2939698083963</v>
+        <v>1.06767797941807</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -11196,10 +11196,10 @@
         <v>8</v>
       </c>
       <c r="C687" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D687">
-        <v>98.33275609934221</v>
+        <v>-1.19947444968797</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -11210,10 +11210,10 @@
         <v>8</v>
       </c>
       <c r="C688" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D688">
-        <v>97.15327981425661</v>
+        <v>1.35330138353935</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -11224,10 +11224,10 @@
         <v>8</v>
       </c>
       <c r="C689" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D689">
-        <v>98.4680564941368</v>
+        <v>0.743339693401657</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -11238,10 +11238,10 @@
         <v>8</v>
       </c>
       <c r="C690" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D690">
-        <v>99.20000864337889</v>
+        <v>0.63830758257053</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -11252,10 +11252,10 @@
         <v>8</v>
       </c>
       <c r="C691" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D691">
-        <v>99.8332098204602</v>
+        <v>-0.703093400986732</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -11266,10 +11266,10 @@
         <v>8</v>
       </c>
       <c r="C692" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D692">
-        <v>99.1312891102193</v>
+        <v>0.518941588932154</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -11280,10 +11280,10 @@
         <v>8</v>
       </c>
       <c r="C693" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D693">
-        <v>99.6457225970568</v>
+        <v>0.688239721296835</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -11294,10 +11294,10 @@
         <v>8</v>
       </c>
       <c r="C694" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D694">
-        <v>100.331524040543</v>
+        <v>-0.897187192827209</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -11308,10 +11308,10 @@
         <v>8</v>
       </c>
       <c r="C695" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D695">
-        <v>99.4313624564829</v>
+        <v>0.754917320277704</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -11322,10 +11322,10 @@
         <v>8</v>
       </c>
       <c r="C696" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D696">
-        <v>100.181987033455</v>
+        <v>-0.245678646881409</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -11336,10 +11336,10 @@
         <v>8</v>
       </c>
       <c r="C697" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D697">
-        <v>99.9358612832923</v>
+        <v>0.359646905011268</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -11350,10 +11350,10 @@
         <v>8</v>
       </c>
       <c r="C698" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D698">
-        <v>100.295277515394</v>
+        <v>0.285699397012995</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -11364,10 +11364,10 @@
         <v>8</v>
       </c>
       <c r="C699" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D699">
-        <v>100.581820518488</v>
+        <v>0.0974740212084102</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -11378,10 +11378,10 @@
         <v>8</v>
       </c>
       <c r="C700" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D700">
-        <v>100.679861663552</v>
+        <v>-0.115273232549551</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -11392,10 +11392,10 @@
         <v>8</v>
       </c>
       <c r="C701" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D701">
-        <v>100.563804732486</v>
+        <v>-0.514181887025378</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -11406,10 +11406,10 @@
         <v>8</v>
       </c>
       <c r="C702" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D702">
-        <v>100.046723863648</v>
+        <v>-0.399185863936824</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -11420,10 +11420,10 @@
         <v>8</v>
       </c>
       <c r="C703" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D703">
-        <v>99.6473514846524</v>
+        <v>0.503023074145426</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -11434,10 +11434,10 @@
         <v>8</v>
       </c>
       <c r="C704" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D704">
-        <v>100.148600655395</v>
+        <v>0.248129287632359</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -11448,10 +11448,10 @@
         <v>8</v>
       </c>
       <c r="C705" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D705">
-        <v>100.397098664775</v>
+        <v>-1.16626139195506</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="C706" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D706">
-        <v>99.22620606440471</v>
+        <v>0.439419874816527</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -11476,10 +11476,10 @@
         <v>8</v>
       </c>
       <c r="C707" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D707">
-        <v>99.66222573487811</v>
+        <v>-0.417925931316065</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -11490,10 +11490,10 @@
         <v>8</v>
       </c>
       <c r="C708" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D708">
-        <v>99.2457114498053</v>
+        <v>0.504375787407274</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -11504,10 +11504,10 @@
         <v>8</v>
       </c>
       <c r="C709" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D709">
-        <v>99.7462827883982</v>
+        <v>-0.209490450096972</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -11518,10 +11518,10 @@
         <v>8</v>
       </c>
       <c r="C710" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D710">
-        <v>99.53732385162979</v>
+        <v>0.105968828252734</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -11532,10 +11532,10 @@
         <v>8</v>
       </c>
       <c r="C711" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D711">
-        <v>99.64280238738949</v>
+        <v>0.434034694726981</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -11546,10 +11546,10 @@
         <v>8</v>
       </c>
       <c r="C712" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D712">
-        <v>100.075286720549</v>
+        <v>-1.01482163011106</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -11560,10 +11560,10 @@
         <v>8</v>
       </c>
       <c r="C713" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D713">
-        <v>99.05970106451321</v>
+        <v>0.205156627383252</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -11574,10 +11574,10 @@
         <v>8</v>
       </c>
       <c r="C714" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D714">
-        <v>99.2629286063131</v>
+        <v>-0.175998025935109</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -11588,10 +11588,10 @@
         <v>8</v>
       </c>
       <c r="C715" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D715">
-        <v>99.08822781148061</v>
+        <v>0.840310917032894</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -11602,10 +11602,10 @@
         <v>8</v>
       </c>
       <c r="C716" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D716">
-        <v>99.9208770072749</v>
+        <v>-1.00806026547431</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -11616,10 +11616,10 @@
         <v>8</v>
       </c>
       <c r="C717" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D717">
-        <v>98.91361434925111</v>
+        <v>-3.28312447152468</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -11630,10 +11630,10 @@
         <v>8</v>
       </c>
       <c r="C718" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D718">
-        <v>95.6661572708813</v>
+        <v>-18.8715240184585</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -11644,10 +11644,10 @@
         <v>8</v>
       </c>
       <c r="C719" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D719">
-        <v>77.6124954239707</v>
+        <v>-1.86576952535115</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -11658,10 +11658,10 @@
         <v>8</v>
       </c>
       <c r="C720" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D720">
-        <v>76.1644251364857</v>
+        <v>11.8552153474137</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -11672,10 +11672,10 @@
         <v>8</v>
       </c>
       <c r="C721" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D721">
-        <v>85.19388175453579</v>
+        <v>5.06443190392565</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -11686,10 +11686,10 @@
         <v>8</v>
       </c>
       <c r="C722" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D722">
-        <v>89.5084678823052</v>
+        <v>2.93545649432239</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -11700,10 +11700,10 @@
         <v>8</v>
       </c>
       <c r="C723" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D723">
-        <v>92.1359500157248</v>
+        <v>2.71215495753072</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -11714,10 +11714,10 @@
         <v>8</v>
       </c>
       <c r="C724" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D724">
-        <v>94.6348197517443</v>
+        <v>1.06498486302344</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -11728,10 +11728,10 @@
         <v>8</v>
       </c>
       <c r="C725" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D725">
-        <v>95.6426662572499</v>
+        <v>0.77341981482455</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -11742,10 +11742,10 @@
         <v>8</v>
       </c>
       <c r="C726" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D726">
-        <v>96.38238558950999</v>
+        <v>-0.294144301304211</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -11756,10 +11756,10 @@
         <v>8</v>
       </c>
       <c r="C727" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D727">
-        <v>96.0988822948374</v>
+        <v>0.0539805083509259</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -11770,10 +11770,10 @@
         <v>8</v>
       </c>
       <c r="C728" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D728">
-        <v>96.15075696001971</v>
+        <v>-0.642745825691715</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -11784,10 +11784,10 @@
         <v>8</v>
       </c>
       <c r="C729" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D729">
-        <v>95.53275198328819</v>
+        <v>1.99021996249591</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -11798,10 +11798,10 @@
         <v>8</v>
       </c>
       <c r="C730" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D730">
-        <v>97.4340638839813</v>
+        <v>-0.189785396341657</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -11812,10 +11812,10 @@
         <v>8</v>
       </c>
       <c r="C731" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D731">
-        <v>97.24914825966729</v>
+        <v>0.00438704145264701</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -11826,10 +11826,10 @@
         <v>8</v>
       </c>
       <c r="C732" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D732">
-        <v>97.2534146201138</v>
+        <v>-0.167710625690121</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -11840,10 +11840,10 @@
         <v>8</v>
       </c>
       <c r="C733" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D733">
-        <v>97.0903103099494</v>
+        <v>-0.353138718993951</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -11854,10 +11854,10 @@
         <v>8</v>
       </c>
       <c r="C734" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D734">
-        <v>96.74744683185359</v>
+        <v>-0.745807330944082</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -11868,10 +11868,10 @@
         <v>8</v>
       </c>
       <c r="C735" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D735">
-        <v>96.0258972808804</v>
+        <v>-0.236336848444096</v>
       </c>
     </row>
     <row r="736" spans="1:4">
@@ -11882,10 +11882,10 @@
         <v>8</v>
       </c>
       <c r="C736" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D736">
-        <v>95.7989527015566</v>
+        <v>0.703696032203438</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -11896,10 +11896,10 @@
         <v>8</v>
       </c>
       <c r="C737" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D737">
-        <v>96.4730861306099</v>
+        <v>0.649428843904287</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -11910,10 +11910,10 @@
         <v>8</v>
       </c>
       <c r="C738" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D738">
-        <v>97.0996101785467</v>
+        <v>0.544029323702389</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -11924,10 +11924,10 @@
         <v>8</v>
       </c>
       <c r="C739" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D739">
-        <v>97.6278605311187</v>
+        <v>0.650823364370035</v>
       </c>
     </row>
     <row r="740" spans="1:4">
@@ -11938,10 +11938,10 @@
         <v>8</v>
       </c>
       <c r="C740" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D740">
-        <v>98.2632454575898</v>
+        <v>0.197573395421569</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -11952,10 +11952,10 @@
         <v>8</v>
       </c>
       <c r="C741" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D741">
-        <v>98.4573874880918</v>
+        <v>0.679671256307635</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -11966,10 +11966,10 @@
         <v>8</v>
       </c>
       <c r="C742" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D742">
-        <v>99.1265740505598</v>
+        <v>0.659553379836608</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -11980,10 +11980,10 @@
         <v>8</v>
       </c>
       <c r="C743" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D743">
-        <v>99.78036672002651</v>
+        <v>0.0262578366863497</v>
       </c>
     </row>
     <row r="744" spans="1:4">
@@ -11994,10 +11994,10 @@
         <v>8</v>
       </c>
       <c r="C744" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D744">
-        <v>99.80656688576489</v>
+        <v>-0.330555071608363</v>
       </c>
     </row>
     <row r="745" spans="1:4">
@@ -12008,10 +12008,10 @@
         <v>8</v>
       </c>
       <c r="C745" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D745">
-        <v>99.47665121712581</v>
+        <v>0.554926142829526</v>
       </c>
     </row>
     <row r="746" spans="1:4">
@@ -12022,10 +12022,10 @@
         <v>8</v>
       </c>
       <c r="C746" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D746">
-        <v>100.028673160741</v>
+        <v>0.492845649044837</v>
       </c>
     </row>
     <row r="747" spans="1:4">
@@ -12036,10 +12036,10 @@
         <v>8</v>
       </c>
       <c r="C747" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D747">
-        <v>100.521660124211</v>
+        <v>0.172300370840461</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -12050,10 +12050,10 @@
         <v>8</v>
       </c>
       <c r="C748" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D748">
-        <v>100.69485931738</v>
+        <v>0.39640801593841</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -12064,10 +12064,10 @@
         <v>8</v>
       </c>
       <c r="C749" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D749">
-        <v>101.094021811352</v>
+        <v>0.559252284660339</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -12078,10 +12078,10 @@
         <v>8</v>
       </c>
       <c r="C750" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D750">
-        <v>101.659392437987</v>
+        <v>0.861930771286601</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -12092,10 +12092,10 @@
         <v>8</v>
       </c>
       <c r="C751" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D751">
-        <v>102.535626023313</v>
+        <v>0.0608511633486408</v>
       </c>
     </row>
     <row r="752" spans="1:4">
@@ -12106,10 +12106,10 @@
         <v>8</v>
       </c>
       <c r="C752" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D752">
-        <v>102.598020144595</v>
+        <v>-0.649170817787048</v>
       </c>
     </row>
     <row r="753" spans="1:4">
@@ -12120,10 +12120,10 @@
         <v>8</v>
       </c>
       <c r="C753" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D753">
-        <v>101.931983738189</v>
+        <v>-0.208194499681358</v>
       </c>
     </row>
     <row r="754" spans="1:4">
@@ -12134,10 +12134,10 @@
         <v>8</v>
       </c>
       <c r="C754" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D754">
-        <v>101.71976695463</v>
+        <v>0.996971532158852</v>
       </c>
     </row>
     <row r="755" spans="1:4">
@@ -12148,10 +12148,10 @@
         <v>8</v>
       </c>
       <c r="C755" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D755">
-        <v>102.733884073746</v>
+        <v>0.17262885494107</v>
       </c>
     </row>
     <row r="756" spans="1:4">
@@ -12162,10 +12162,10 @@
         <v>8</v>
       </c>
       <c r="C756" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D756">
-        <v>102.911232401459</v>
+        <v>0.429127295928433</v>
       </c>
     </row>
     <row r="757" spans="1:4">
@@ -12176,10 +12176,10 @@
         <v>8</v>
       </c>
       <c r="C757" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D757">
-        <v>103.35285259027</v>
+        <v>0.0214137020598137</v>
       </c>
     </row>
     <row r="758" spans="1:4">
@@ -12190,10 +12190,10 @@
         <v>8</v>
       </c>
       <c r="C758" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D758">
-        <v>103.374984262194</v>
+        <v>0.333308097553942</v>
       </c>
     </row>
     <row r="759" spans="1:4">
@@ -12204,10 +12204,10 @@
         <v>8</v>
       </c>
       <c r="C759" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D759">
-        <v>103.719541455585</v>
+        <v>0.839259449457508</v>
       </c>
     </row>
     <row r="760" spans="1:4">
@@ -12218,10 +12218,10 @@
         <v>8</v>
       </c>
       <c r="C760" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D760">
-        <v>104.590017508185</v>
+        <v>0.028556904948096</v>
       </c>
     </row>
     <row r="761" spans="1:4">
@@ -12232,10 +12232,10 @@
         <v>8</v>
       </c>
       <c r="C761" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D761">
-        <v>104.61988518007</v>
+        <v>-0.734989349571069</v>
       </c>
     </row>
     <row r="762" spans="1:4">
@@ -12246,10 +12246,10 @@
         <v>8</v>
       </c>
       <c r="C762" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D762">
-        <v>103.850940166463</v>
+        <v>0.422643385143595</v>
       </c>
     </row>
     <row r="763" spans="1:4">
@@ -12260,10 +12260,10 @@
         <v>8</v>
       </c>
       <c r="C763" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D763">
-        <v>104.289859295486</v>
+        <v>0.0317834279937923</v>
       </c>
     </row>
     <row r="764" spans="1:4">
@@ -12274,10 +12274,10 @@
         <v>8</v>
       </c>
       <c r="C764" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D764">
-        <v>104.32300618782</v>
+        <v>0.335327522274609</v>
       </c>
     </row>
     <row r="765" spans="1:4">
@@ -12288,10 +12288,10 @@
         <v>8</v>
       </c>
       <c r="C765" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D765">
-        <v>104.672829939632</v>
+        <v>0.258301600458255</v>
       </c>
     </row>
     <row r="766" spans="1:4">
@@ -12302,10 +12302,10 @@
         <v>8</v>
       </c>
       <c r="C766" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D766">
-        <v>104.943201534611</v>
+        <v>-1.29286934111642</v>
       </c>
     </row>
     <row r="767" spans="1:4">
@@ -12316,10 +12316,10 @@
         <v>8</v>
       </c>
       <c r="C767" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D767">
-        <v>103.586423056384</v>
+        <v>0.81626037315794</v>
       </c>
     </row>
     <row r="768" spans="1:4">
@@ -12330,10 +12330,10 @@
         <v>8</v>
       </c>
       <c r="C768" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D768">
-        <v>104.431957979765</v>
+        <v>0.15077136242001</v>
       </c>
     </row>
     <row r="769" spans="1:4">
@@ -12344,10 +12344,10 @@
         <v>8</v>
       </c>
       <c r="C769" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D769">
-        <v>104.589411465613</v>
+        <v>1.00418971096161</v>
       </c>
     </row>
     <row r="770" spans="1:4">
@@ -12358,10 +12358,10 @@
         <v>8</v>
       </c>
       <c r="C770" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D770">
-        <v>105.639687574306</v>
+        <v>-0.8311450163097091</v>
       </c>
     </row>
     <row r="771" spans="1:4">
@@ -12372,10 +12372,10 @@
         <v>8</v>
       </c>
       <c r="C771" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D771">
-        <v>104.761668575787</v>
+        <v>0.24652045448299</v>
       </c>
     </row>
     <row r="772" spans="1:4">
@@ -12386,10 +12386,10 @@
         <v>8</v>
       </c>
       <c r="C772" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D772">
-        <v>105.019927517284</v>
+        <v>-0.957568238433126</v>
       </c>
     </row>
     <row r="773" spans="1:4">
@@ -12400,10 +12400,10 @@
         <v>8</v>
       </c>
       <c r="C773" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D773">
-        <v>104.014290047353</v>
+        <v>0.47154692022866</v>
       </c>
     </row>
     <row r="774" spans="1:4">
@@ -12414,10 +12414,10 @@
         <v>8</v>
       </c>
       <c r="C774" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D774">
-        <v>104.504766228669</v>
+        <v>-0.929280372056929</v>
       </c>
     </row>
     <row r="775" spans="1:4">
@@ -12428,10 +12428,10 @@
         <v>8</v>
       </c>
       <c r="C775" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D775">
-        <v>103.533623948242</v>
+        <v>0.73491051533594</v>
       </c>
     </row>
     <row r="776" spans="1:4">
@@ -12442,10 +12442,10 @@
         <v>8</v>
       </c>
       <c r="C776" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D776">
-        <v>104.294503437546</v>
+        <v>0.948250835299502</v>
       </c>
     </row>
     <row r="777" spans="1:4">
@@ -12456,10 +12456,10 @@
         <v>8</v>
       </c>
       <c r="C777" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D777">
-        <v>105.283476937564</v>
+        <v>-0.292047383306249</v>
       </c>
     </row>
     <row r="778" spans="1:4">
@@ -12470,10 +12470,10 @@
         <v>8</v>
       </c>
       <c r="C778" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D778">
-        <v>104.975999298114</v>
+        <v>-0.282126271786132</v>
       </c>
     </row>
     <row r="779" spans="1:4">
@@ -12484,10 +12484,10 @@
         <v>8</v>
       </c>
       <c r="C779" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D779">
-        <v>104.679834425024</v>
+        <v>0.189066664917936</v>
       </c>
     </row>
     <row r="780" spans="1:4">
@@ -12498,10 +12498,10 @@
         <v>8</v>
       </c>
       <c r="C780" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D780">
-        <v>104.877749096813</v>
+        <v>0.166639346313269</v>
       </c>
     </row>
     <row r="781" spans="1:4">
@@ -12512,10 +12512,10 @@
         <v>8</v>
       </c>
       <c r="C781" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D781">
-        <v>105.052516692336</v>
+        <v>-0.550297392419519</v>
       </c>
     </row>
     <row r="782" spans="1:4">
@@ -12526,10 +12526,10 @@
         <v>8</v>
       </c>
       <c r="C782" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D782">
-        <v>104.474415432307</v>
+        <v>0.474921123856875</v>
       </c>
     </row>
     <row r="783" spans="1:4">
@@ -12540,10 +12540,10 @@
         <v>8</v>
       </c>
       <c r="C783" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D783">
-        <v>104.970586500221</v>
+        <v>-0.437056003877845</v>
       </c>
     </row>
     <row r="784" spans="1:4">
@@ -12554,10 +12554,10 @@
         <v>8</v>
       </c>
       <c r="C784" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D784">
-        <v>104.511806249616</v>
+        <v>0.978663246992495</v>
       </c>
     </row>
     <row r="785" spans="1:4">
@@ -12568,10 +12568,10 @@
         <v>8</v>
       </c>
       <c r="C785" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D785">
-        <v>105.534624886149</v>
+        <v>-0.0862251333182518</v>
       </c>
     </row>
     <row r="786" spans="1:4">
@@ -12582,10 +12582,10 @@
         <v>8</v>
       </c>
       <c r="C786" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D786">
-        <v>105.443627515144</v>
+        <v>0.393671729628586</v>
       </c>
     </row>
     <row r="787" spans="1:4">
@@ -12596,10 +12596,10 @@
         <v>8</v>
       </c>
       <c r="C787" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D787">
-        <v>105.858729267366</v>
+        <v>-1.00989027495494</v>
       </c>
     </row>
     <row r="788" spans="1:4">
@@ -12610,10 +12610,10 @@
         <v>8</v>
       </c>
       <c r="C788" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D788">
-        <v>104.789672255304</v>
+        <v>0.280673190736236</v>
       </c>
     </row>
     <row r="789" spans="1:4">
@@ -12624,10 +12624,10 @@
         <v>8</v>
       </c>
       <c r="C789" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D789">
-        <v>105.083788771985</v>
+        <v>0.485302413528843</v>
       </c>
     </row>
     <row r="790" spans="1:4">
@@ -12638,10 +12638,10 @@
         <v>8</v>
       </c>
       <c r="C790" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D790">
-        <v>105.593762935123</v>
+        <v>1.64421504467336</v>
       </c>
     </row>
     <row r="791" spans="1:4">
@@ -12652,10 +12652,10 @@
         <v>8</v>
       </c>
       <c r="C791" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D791">
-        <v>107.329951471539</v>
+        <v>-0.443561089393807</v>
       </c>
     </row>
     <row r="792" spans="1:4">
@@ -12666,24 +12666,24 @@
         <v>8</v>
       </c>
       <c r="C792" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D792">
-        <v>106.853877569546</v>
+        <v>-0.0584933562905232</v>
       </c>
     </row>
     <row r="793" spans="1:4">
       <c r="A793" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B793" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C793" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D793">
-        <v>106.791375150229</v>
+        <v>56.2778528191742</v>
       </c>
     </row>
     <row r="794" spans="1:4">
@@ -12694,10 +12694,10 @@
         <v>9</v>
       </c>
       <c r="C794" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D794">
-        <v>2.53094689127942</v>
+        <v>57.7022153855799</v>
       </c>
     </row>
     <row r="795" spans="1:4">
@@ -12708,10 +12708,10 @@
         <v>9</v>
       </c>
       <c r="C795" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D795">
-        <v>0.19002275222193</v>
+        <v>57.8118627233486</v>
       </c>
     </row>
     <row r="796" spans="1:4">
@@ -12722,10 +12722,10 @@
         <v>9</v>
       </c>
       <c r="C796" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D796">
-        <v>-1.08698892937487</v>
+        <v>57.1834541756804</v>
       </c>
     </row>
     <row r="797" spans="1:4">
@@ -12736,10 +12736,10 @@
         <v>9</v>
       </c>
       <c r="C797" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D797">
-        <v>1.21488838719286</v>
+        <v>57.8781693198565</v>
       </c>
     </row>
     <row r="798" spans="1:4">
@@ -12750,10 +12750,10 @@
         <v>9</v>
       </c>
       <c r="C798" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D798">
-        <v>-0.757029604935477</v>
+        <v>57.4400144433105</v>
       </c>
     </row>
     <row r="799" spans="1:4">
@@ -12764,10 +12764,10 @@
         <v>9</v>
       </c>
       <c r="C799" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D799">
-        <v>1.51307500924125</v>
+        <v>58.3091249471568</v>
       </c>
     </row>
     <row r="800" spans="1:4">
@@ -12778,10 +12778,10 @@
         <v>9</v>
       </c>
       <c r="C800" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D800">
-        <v>-0.383129663069814</v>
+        <v>58.0857253932078</v>
       </c>
     </row>
     <row r="801" spans="1:4">
@@ -12792,10 +12792,10 @@
         <v>9</v>
       </c>
       <c r="C801" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D801">
-        <v>-0.425961080502124</v>
+        <v>57.8383028097054</v>
       </c>
     </row>
     <row r="802" spans="1:4">
@@ -12806,10 +12806,10 @@
         <v>9</v>
       </c>
       <c r="C802" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D802">
-        <v>-0.147602148384218</v>
+        <v>57.7529322321693</v>
       </c>
     </row>
     <row r="803" spans="1:4">
@@ -12820,10 +12820,10 @@
         <v>9</v>
       </c>
       <c r="C803" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D803">
-        <v>-0.246182545801388</v>
+        <v>57.6107545933252</v>
       </c>
     </row>
     <row r="804" spans="1:4">
@@ -12834,10 +12834,10 @@
         <v>9</v>
       </c>
       <c r="C804" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D804">
-        <v>1.51048424248243</v>
+        <v>58.4809559634326</v>
       </c>
     </row>
     <row r="805" spans="1:4">
@@ -12851,7 +12851,7 @@
         <v>10</v>
       </c>
       <c r="D805">
-        <v>0.443921507457445</v>
+        <v>58.740565504721</v>
       </c>
     </row>
     <row r="806" spans="1:4">
@@ -12865,7 +12865,7 @@
         <v>11</v>
       </c>
       <c r="D806">
-        <v>-0.0540930616349744</v>
+        <v>58.7087909344178</v>
       </c>
     </row>
     <row r="807" spans="1:4">
@@ -12879,7 +12879,7 @@
         <v>12</v>
       </c>
       <c r="D807">
-        <v>0.821981539894723</v>
+        <v>59.1913663581941</v>
       </c>
     </row>
     <row r="808" spans="1:4">
@@ -12893,7 +12893,7 @@
         <v>13</v>
       </c>
       <c r="D808">
-        <v>2.07027841107363</v>
+        <v>60.4167924371273</v>
       </c>
     </row>
     <row r="809" spans="1:4">
@@ -12907,7 +12907,7 @@
         <v>14</v>
       </c>
       <c r="D809">
-        <v>-0.120586173711745</v>
+        <v>60.343938138848</v>
       </c>
     </row>
     <row r="810" spans="1:4">
@@ -12921,7 +12921,7 @@
         <v>15</v>
       </c>
       <c r="D810">
-        <v>0.136582775118277</v>
+        <v>60.4263575641737</v>
       </c>
     </row>
     <row r="811" spans="1:4">
@@ -12935,7 +12935,7 @@
         <v>16</v>
       </c>
       <c r="D811">
-        <v>-0.801470305041418</v>
+        <v>59.9420582518787</v>
       </c>
     </row>
     <row r="812" spans="1:4">
@@ -12949,7 +12949,7 @@
         <v>17</v>
       </c>
       <c r="D812">
-        <v>0.8501986066621779</v>
+        <v>60.4516847959408</v>
       </c>
     </row>
     <row r="813" spans="1:4">
@@ -12963,7 +12963,7 @@
         <v>18</v>
       </c>
       <c r="D813">
-        <v>0.700612252016408</v>
+        <v>60.8752167061715</v>
       </c>
     </row>
     <row r="814" spans="1:4">
@@ -12977,7 +12977,7 @@
         <v>19</v>
       </c>
       <c r="D814">
-        <v>0.345851090951355</v>
+        <v>61.0857543072688</v>
       </c>
     </row>
     <row r="815" spans="1:4">
@@ -12991,7 +12991,7 @@
         <v>20</v>
       </c>
       <c r="D815">
-        <v>0.36985199048809</v>
+        <v>61.3116811854789</v>
       </c>
     </row>
     <row r="816" spans="1:4">
@@ -13005,7 +13005,7 @@
         <v>21</v>
       </c>
       <c r="D816">
-        <v>-0.863394507473358</v>
+        <v>60.7823194976839</v>
       </c>
     </row>
     <row r="817" spans="1:4">
@@ -13019,7 +13019,7 @@
         <v>22</v>
       </c>
       <c r="D817">
-        <v>0.199014030411448</v>
+        <v>60.9032848414938</v>
       </c>
     </row>
     <row r="818" spans="1:4">
@@ -13033,7 +13033,7 @@
         <v>23</v>
       </c>
       <c r="D818">
-        <v>-6.41657570082118</v>
+        <v>56.9953794653526</v>
       </c>
     </row>
     <row r="819" spans="1:4">
@@ -13047,7 +13047,7 @@
         <v>24</v>
       </c>
       <c r="D819">
-        <v>-0.487545236307307</v>
+        <v>56.717501207854</v>
       </c>
     </row>
     <row r="820" spans="1:4">
@@ -13061,7 +13061,7 @@
         <v>25</v>
       </c>
       <c r="D820">
-        <v>-2.84520769312689</v>
+        <v>55.1037705001388</v>
       </c>
     </row>
     <row r="821" spans="1:4">
@@ -13075,7 +13075,7 @@
         <v>26</v>
       </c>
       <c r="D821">
-        <v>-0.747534777167125</v>
+        <v>54.6918506521199</v>
       </c>
     </row>
     <row r="822" spans="1:4">
@@ -13089,7 +13089,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>1.11153272839475</v>
+        <v>55.299768471883</v>
       </c>
     </row>
     <row r="823" spans="1:4">
@@ -13103,7 +13103,7 @@
         <v>28</v>
       </c>
       <c r="D823">
-        <v>0.718944024399404</v>
+        <v>55.6973428528183</v>
       </c>
     </row>
     <row r="824" spans="1:4">
@@ -13117,7 +13117,7 @@
         <v>29</v>
       </c>
       <c r="D824">
-        <v>0.7724314799334</v>
+        <v>56.1275666624999</v>
       </c>
     </row>
     <row r="825" spans="1:4">
@@ -13131,7 +13131,7 @@
         <v>30</v>
       </c>
       <c r="D825">
-        <v>0.8680253561186509</v>
+        <v>56.6147681729028</v>
       </c>
     </row>
     <row r="826" spans="1:4">
@@ -13145,7 +13145,7 @@
         <v>31</v>
       </c>
       <c r="D826">
-        <v>-2.16042856197637</v>
+        <v>55.3916465509987</v>
       </c>
     </row>
     <row r="827" spans="1:4">
@@ -13159,7 +13159,7 @@
         <v>32</v>
       </c>
       <c r="D827">
-        <v>3.1996443816434</v>
+        <v>57.1639822577675</v>
       </c>
     </row>
     <row r="828" spans="1:4">
@@ -13173,7 +13173,7 @@
         <v>33</v>
       </c>
       <c r="D828">
-        <v>3.58138611518464</v>
+        <v>59.2112451812338</v>
       </c>
     </row>
     <row r="829" spans="1:4">
@@ -13187,7 +13187,7 @@
         <v>34</v>
       </c>
       <c r="D829">
-        <v>-0.127338791715359</v>
+        <v>59.1358462970604</v>
       </c>
     </row>
     <row r="830" spans="1:4">
@@ -13201,7 +13201,7 @@
         <v>35</v>
       </c>
       <c r="D830">
-        <v>-0.882764191696606</v>
+        <v>58.6138162214932</v>
       </c>
     </row>
     <row r="831" spans="1:4">
@@ -13215,7 +13215,7 @@
         <v>36</v>
       </c>
       <c r="D831">
-        <v>0.859296483650573</v>
+        <v>59.1174826832179</v>
       </c>
     </row>
     <row r="832" spans="1:4">
@@ -13229,7 +13229,7 @@
         <v>37</v>
       </c>
       <c r="D832">
-        <v>-0.488401709124475</v>
+        <v>58.8287518874017</v>
       </c>
     </row>
     <row r="833" spans="1:4">
@@ -13243,7 +13243,7 @@
         <v>38</v>
       </c>
       <c r="D833">
-        <v>1.34504671716764</v>
+        <v>59.6200260834139</v>
       </c>
     </row>
     <row r="834" spans="1:4">
@@ -13257,7 +13257,7 @@
         <v>39</v>
       </c>
       <c r="D834">
-        <v>0.84112475694087</v>
+        <v>60.1215048828961</v>
       </c>
     </row>
     <row r="835" spans="1:4">
@@ -13271,7 +13271,7 @@
         <v>40</v>
       </c>
       <c r="D835">
-        <v>0.0508216560550334</v>
+        <v>60.1520596273228</v>
       </c>
     </row>
     <row r="836" spans="1:4">
@@ -13285,7 +13285,7 @@
         <v>41</v>
       </c>
       <c r="D836">
-        <v>0.0368806808984434</v>
+        <v>60.1742441164878</v>
       </c>
     </row>
     <row r="837" spans="1:4">
@@ -13299,7 +13299,7 @@
         <v>42</v>
       </c>
       <c r="D837">
-        <v>0.780498148543285</v>
+        <v>60.6439029777169</v>
       </c>
     </row>
     <row r="838" spans="1:4">
@@ -13313,7 +13313,7 @@
         <v>43</v>
       </c>
       <c r="D838">
-        <v>0.809934014103919</v>
+        <v>61.1350785754136</v>
       </c>
     </row>
     <row r="839" spans="1:4">
@@ -13327,7 +13327,7 @@
         <v>44</v>
       </c>
       <c r="D839">
-        <v>1.28395285360487</v>
+        <v>61.9200241613362</v>
       </c>
     </row>
     <row r="840" spans="1:4">
@@ -13341,7 +13341,7 @@
         <v>45</v>
       </c>
       <c r="D840">
-        <v>0.679515481429394</v>
+        <v>62.3407803116173</v>
       </c>
     </row>
     <row r="841" spans="1:4">
@@ -13355,7 +13355,7 @@
         <v>46</v>
       </c>
       <c r="D841">
-        <v>-0.522854190395916</v>
+        <v>62.0148289294325</v>
       </c>
     </row>
     <row r="842" spans="1:4">
@@ -13369,7 +13369,7 @@
         <v>47</v>
       </c>
       <c r="D842">
-        <v>0.396025310901638</v>
+        <v>62.2604233485054</v>
       </c>
     </row>
     <row r="843" spans="1:4">
@@ -13383,7 +13383,7 @@
         <v>48</v>
       </c>
       <c r="D843">
-        <v>0.59041483275093</v>
+        <v>62.6280181228885</v>
       </c>
     </row>
     <row r="844" spans="1:4">
@@ -13397,7 +13397,7 @@
         <v>49</v>
       </c>
       <c r="D844">
-        <v>1.07017920144283</v>
+        <v>63.2982501471155</v>
       </c>
     </row>
     <row r="845" spans="1:4">
@@ -13411,7 +13411,7 @@
         <v>50</v>
       </c>
       <c r="D845">
-        <v>0.9746307341107709</v>
+        <v>63.9151743472036</v>
       </c>
     </row>
     <row r="846" spans="1:4">
@@ -13425,7 +13425,7 @@
         <v>51</v>
       </c>
       <c r="D846">
-        <v>1.05161746950597</v>
+        <v>64.587317486304</v>
       </c>
     </row>
     <row r="847" spans="1:4">
@@ -13439,7 +13439,7 @@
         <v>52</v>
       </c>
       <c r="D847">
-        <v>-0.020540643098732</v>
+        <v>64.5740508359321</v>
       </c>
     </row>
     <row r="848" spans="1:4">
@@ -13453,7 +13453,7 @@
         <v>53</v>
       </c>
       <c r="D848">
-        <v>0.815585776316596</v>
+        <v>65.10070760974141</v>
       </c>
     </row>
     <row r="849" spans="1:4">
@@ -13467,7 +13467,7 @@
         <v>54</v>
       </c>
       <c r="D849">
-        <v>0.510619492536146</v>
+        <v>65.4331245125757</v>
       </c>
     </row>
     <row r="850" spans="1:4">
@@ -13481,7 +13481,7 @@
         <v>55</v>
       </c>
       <c r="D850">
-        <v>1.42086610161176</v>
+        <v>66.3628415980003</v>
       </c>
     </row>
     <row r="851" spans="1:4">
@@ -13495,7 +13495,7 @@
         <v>56</v>
       </c>
       <c r="D851">
-        <v>0.899090192482155</v>
+        <v>66.9595033982604</v>
       </c>
     </row>
     <row r="852" spans="1:4">
@@ -13509,7 +13509,7 @@
         <v>57</v>
       </c>
       <c r="D852">
-        <v>-0.319373354502583</v>
+        <v>66.7456525860991</v>
       </c>
     </row>
     <row r="853" spans="1:4">
@@ -13523,7 +13523,7 @@
         <v>58</v>
       </c>
       <c r="D853">
-        <v>0.647424248228567</v>
+        <v>67.1777801255799</v>
       </c>
     </row>
     <row r="854" spans="1:4">
@@ -13537,7 +13537,7 @@
         <v>59</v>
       </c>
       <c r="D854">
-        <v>1.27880525083828</v>
+        <v>68.03685310522241</v>
       </c>
     </row>
     <row r="855" spans="1:4">
@@ -13551,7 +13551,7 @@
         <v>60</v>
       </c>
       <c r="D855">
-        <v>0.823238215993127</v>
+        <v>68.5969584809437</v>
       </c>
     </row>
     <row r="856" spans="1:4">
@@ -13565,7 +13565,7 @@
         <v>61</v>
       </c>
       <c r="D856">
-        <v>-0.00654804318145352</v>
+        <v>68.59246672248121</v>
       </c>
     </row>
     <row r="857" spans="1:4">
@@ -13579,7 +13579,7 @@
         <v>62</v>
       </c>
       <c r="D857">
-        <v>-0.133427115099227</v>
+        <v>68.500945772958</v>
       </c>
     </row>
     <row r="858" spans="1:4">
@@ -13593,7 +13593,7 @@
         <v>63</v>
       </c>
       <c r="D858">
-        <v>-0.508565339857736</v>
+        <v>68.15257370528199</v>
       </c>
     </row>
     <row r="859" spans="1:4">
@@ -13607,7 +13607,7 @@
         <v>64</v>
       </c>
       <c r="D859">
-        <v>0.696973759778197</v>
+        <v>68.6275792606213</v>
       </c>
     </row>
     <row r="860" spans="1:4">
@@ -13621,7 +13621,7 @@
         <v>65</v>
       </c>
       <c r="D860">
-        <v>0.39013934657568</v>
+        <v>68.89532244991941</v>
       </c>
     </row>
     <row r="861" spans="1:4">
@@ -13635,7 +13635,7 @@
         <v>66</v>
       </c>
       <c r="D861">
-        <v>-0.412047380414771</v>
+        <v>68.6114410785362</v>
       </c>
     </row>
     <row r="862" spans="1:4">
@@ -13649,7 +13649,7 @@
         <v>67</v>
       </c>
       <c r="D862">
-        <v>-0.12633513228002</v>
+        <v>68.52476072369041</v>
       </c>
     </row>
     <row r="863" spans="1:4">
@@ -13663,7 +13663,7 @@
         <v>68</v>
       </c>
       <c r="D863">
-        <v>0.181581639670525</v>
+        <v>68.64918910779279</v>
       </c>
     </row>
     <row r="864" spans="1:4">
@@ -13677,7 +13677,7 @@
         <v>69</v>
       </c>
       <c r="D864">
-        <v>0.545080870952108</v>
+        <v>69.0233827056831</v>
       </c>
     </row>
     <row r="865" spans="1:4">
@@ -13691,7 +13691,7 @@
         <v>70</v>
       </c>
       <c r="D865">
-        <v>0.749080180263917</v>
+        <v>69.5404231852791</v>
       </c>
     </row>
     <row r="866" spans="1:4">
@@ -13705,7 +13705,7 @@
         <v>71</v>
       </c>
       <c r="D866">
-        <v>-0.139111828016136</v>
+        <v>69.4436842313759</v>
       </c>
     </row>
     <row r="867" spans="1:4">
@@ -13719,7 +13719,7 @@
         <v>72</v>
       </c>
       <c r="D867">
-        <v>0.340507508033627</v>
+        <v>69.6801451900389</v>
       </c>
     </row>
     <row r="868" spans="1:4">
@@ -13733,7 +13733,7 @@
         <v>73</v>
       </c>
       <c r="D868">
-        <v>0.226785481006986</v>
+        <v>69.8381696424745</v>
       </c>
     </row>
     <row r="869" spans="1:4">
@@ -13747,7 +13747,7 @@
         <v>74</v>
       </c>
       <c r="D869">
-        <v>0.387052070042371</v>
+        <v>70.10847972375539</v>
       </c>
     </row>
     <row r="870" spans="1:4">
@@ -13761,7 +13761,7 @@
         <v>75</v>
       </c>
       <c r="D870">
-        <v>-0.432126486948825</v>
+        <v>69.8055224132719</v>
       </c>
     </row>
     <row r="871" spans="1:4">
@@ -13775,7 +13775,7 @@
         <v>76</v>
       </c>
       <c r="D871">
-        <v>0.776100043415617</v>
+        <v>70.34728310302781</v>
       </c>
     </row>
     <row r="872" spans="1:4">
@@ -13789,7 +13789,7 @@
         <v>77</v>
       </c>
       <c r="D872">
-        <v>-0.13065170893678</v>
+        <v>70.25537317546311</v>
       </c>
     </row>
     <row r="873" spans="1:4">
@@ -13803,7 +13803,7 @@
         <v>78</v>
       </c>
       <c r="D873">
-        <v>0.942425891683873</v>
+        <v>70.9174780025678</v>
       </c>
     </row>
     <row r="874" spans="1:4">
@@ -13817,7 +13817,7 @@
         <v>79</v>
       </c>
       <c r="D874">
-        <v>-0.146426323042448</v>
+        <v>70.8136361471342</v>
       </c>
     </row>
     <row r="875" spans="1:4">
@@ -13831,7 +13831,7 @@
         <v>80</v>
       </c>
       <c r="D875">
-        <v>0.264661329963878</v>
+        <v>71.00105245835699</v>
       </c>
     </row>
     <row r="876" spans="1:4">
@@ -13845,7 +13845,7 @@
         <v>81</v>
       </c>
       <c r="D876">
-        <v>0.937254445636992</v>
+        <v>71.66651297897199</v>
       </c>
     </row>
     <row r="877" spans="1:4">
@@ -13859,7 +13859,7 @@
         <v>82</v>
       </c>
       <c r="D877">
-        <v>2.74734105430052</v>
+        <v>73.63543651222891</v>
       </c>
     </row>
     <row r="878" spans="1:4">
@@ -13873,7 +13873,7 @@
         <v>83</v>
       </c>
       <c r="D878">
-        <v>-0.613676711328603</v>
+        <v>73.1835529870682</v>
       </c>
     </row>
     <row r="879" spans="1:4">
@@ -13887,7 +13887,7 @@
         <v>84</v>
       </c>
       <c r="D879">
-        <v>-0.117439265239538</v>
+        <v>73.097606760164</v>
       </c>
     </row>
     <row r="880" spans="1:4">
@@ -13901,7 +13901,7 @@
         <v>85</v>
       </c>
       <c r="D880">
-        <v>0.199908982273334</v>
+        <v>73.24373544190441</v>
       </c>
     </row>
     <row r="881" spans="1:4">
@@ -13915,7 +13915,7 @@
         <v>86</v>
       </c>
       <c r="D881">
-        <v>0.764371930675578</v>
+        <v>73.80358999660061</v>
       </c>
     </row>
     <row r="882" spans="1:4">
@@ -13929,7 +13929,7 @@
         <v>87</v>
       </c>
       <c r="D882">
-        <v>0.739145311811273</v>
+        <v>74.3491057720089</v>
       </c>
     </row>
     <row r="883" spans="1:4">
@@ -13943,7 +13943,7 @@
         <v>88</v>
       </c>
       <c r="D883">
-        <v>0.5578594659964911</v>
+        <v>74.7638692964418</v>
       </c>
     </row>
     <row r="884" spans="1:4">
@@ -13957,7 +13957,7 @@
         <v>89</v>
       </c>
       <c r="D884">
-        <v>-0.5541969596076221</v>
+        <v>74.3495302059159</v>
       </c>
     </row>
     <row r="885" spans="1:4">
@@ -13971,7 +13971,7 @@
         <v>90</v>
       </c>
       <c r="D885">
-        <v>-0.0203502710159675</v>
+        <v>74.3343998750199</v>
       </c>
     </row>
     <row r="886" spans="1:4">
@@ -13985,7 +13985,7 @@
         <v>91</v>
       </c>
       <c r="D886">
-        <v>0.100605256545738</v>
+        <v>74.4091841887159</v>
       </c>
     </row>
     <row r="887" spans="1:4">
@@ -13999,7 +13999,7 @@
         <v>92</v>
       </c>
       <c r="D887">
-        <v>-0.317558334113321</v>
+        <v>74.1728916229789</v>
       </c>
     </row>
     <row r="888" spans="1:4">
@@ -14013,7 +14013,7 @@
         <v>93</v>
       </c>
       <c r="D888">
-        <v>-0.9133467291890131</v>
+        <v>73.49543594339551</v>
       </c>
     </row>
     <row r="889" spans="1:4">
@@ -14027,7 +14027,7 @@
         <v>94</v>
       </c>
       <c r="D889">
-        <v>0.929402111921851</v>
+        <v>74.1785040772196</v>
       </c>
     </row>
     <row r="890" spans="1:4">
@@ -14041,7 +14041,7 @@
         <v>95</v>
       </c>
       <c r="D890">
-        <v>-0.813318884051717</v>
+        <v>73.5751962956525</v>
       </c>
     </row>
     <row r="891" spans="1:4">
@@ -14055,7 +14055,7 @@
         <v>96</v>
       </c>
       <c r="D891">
-        <v>-0.200771384870413</v>
+        <v>73.4274783551286</v>
       </c>
     </row>
     <row r="892" spans="1:4">
@@ -14069,7 +14069,7 @@
         <v>97</v>
       </c>
       <c r="D892">
-        <v>-0.216454180735726</v>
+        <v>73.2685415084201</v>
       </c>
     </row>
     <row r="893" spans="1:4">
@@ -14083,7 +14083,7 @@
         <v>98</v>
       </c>
       <c r="D893">
-        <v>-0.128052902384201</v>
+        <v>73.174719014484</v>
       </c>
     </row>
     <row r="894" spans="1:4">
@@ -14097,7 +14097,7 @@
         <v>99</v>
       </c>
       <c r="D894">
-        <v>0.09342337018944941</v>
+        <v>73.243081303114</v>
       </c>
     </row>
     <row r="895" spans="1:4">
@@ -14111,7 +14111,7 @@
         <v>100</v>
       </c>
       <c r="D895">
-        <v>-0.169680963476093</v>
+        <v>73.11880173707929</v>
       </c>
     </row>
     <row r="896" spans="1:4">
@@ -14125,7 +14125,7 @@
         <v>101</v>
       </c>
       <c r="D896">
-        <v>0.52618627742651</v>
+        <v>73.5035428380385</v>
       </c>
     </row>
     <row r="897" spans="1:4">
@@ -14139,7 +14139,7 @@
         <v>102</v>
       </c>
       <c r="D897">
-        <v>-0.127108644691543</v>
+        <v>73.4101134809368</v>
       </c>
     </row>
     <row r="898" spans="1:4">
@@ -14153,7 +14153,7 @@
         <v>103</v>
       </c>
       <c r="D898">
-        <v>-1.12400670904435</v>
+        <v>72.584978880294</v>
       </c>
     </row>
     <row r="899" spans="1:4">
@@ -14167,7 +14167,7 @@
         <v>104</v>
       </c>
       <c r="D899">
-        <v>0.396137551714659</v>
+        <v>72.872515238543</v>
       </c>
     </row>
     <row r="900" spans="1:4">
@@ -14181,7 +14181,7 @@
         <v>105</v>
       </c>
       <c r="D900">
-        <v>-0.221202511296659</v>
+        <v>72.7113194047903</v>
       </c>
     </row>
     <row r="901" spans="1:4">
@@ -14195,7 +14195,7 @@
         <v>106</v>
       </c>
       <c r="D901">
-        <v>-1.20863640065264</v>
+        <v>71.8325039310692</v>
       </c>
     </row>
     <row r="902" spans="1:4">
@@ -14209,7 +14209,7 @@
         <v>107</v>
       </c>
       <c r="D902">
-        <v>-0.105053147262013</v>
+        <v>71.7570416249325</v>
       </c>
     </row>
     <row r="903" spans="1:4">
@@ -14223,7 +14223,7 @@
         <v>108</v>
       </c>
       <c r="D903">
-        <v>0.84170185747825</v>
+        <v>72.361021977161</v>
       </c>
     </row>
     <row r="904" spans="1:4">
@@ -14237,7 +14237,7 @@
         <v>109</v>
       </c>
       <c r="D904">
-        <v>0.779846659878713</v>
+        <v>72.925326990104</v>
       </c>
     </row>
     <row r="905" spans="1:4">
@@ -14251,7 +14251,7 @@
         <v>110</v>
       </c>
       <c r="D905">
-        <v>0.0599001663699639</v>
+        <v>72.9690093822969</v>
       </c>
     </row>
     <row r="906" spans="1:4">
@@ -14265,7 +14265,7 @@
         <v>111</v>
       </c>
       <c r="D906">
-        <v>-0.07921391473217911</v>
+        <v>72.9112077734239</v>
       </c>
     </row>
     <row r="907" spans="1:4">
@@ -14279,7 +14279,7 @@
         <v>112</v>
       </c>
       <c r="D907">
-        <v>0.392631990984449</v>
+        <v>73.19748050015551</v>
       </c>
     </row>
     <row r="908" spans="1:4">
@@ -14293,7 +14293,7 @@
         <v>113</v>
       </c>
       <c r="D908">
-        <v>0.812807510240776</v>
+        <v>73.7924351189678</v>
       </c>
     </row>
     <row r="909" spans="1:4">
@@ -14307,7 +14307,7 @@
         <v>114</v>
       </c>
       <c r="D909">
-        <v>-0.248639901277825</v>
+        <v>73.6089576811375</v>
       </c>
     </row>
     <row r="910" spans="1:4">
@@ -14321,7 +14321,7 @@
         <v>115</v>
       </c>
       <c r="D910">
-        <v>0.480842598246167</v>
+        <v>73.9629009057934</v>
       </c>
     </row>
     <row r="911" spans="1:4">
@@ -14335,7 +14335,7 @@
         <v>116</v>
       </c>
       <c r="D911">
-        <v>-0.603282281516837</v>
+        <v>73.5166958297329</v>
       </c>
     </row>
     <row r="912" spans="1:4">
@@ -14349,7 +14349,7 @@
         <v>117</v>
       </c>
       <c r="D912">
-        <v>0.0635157909927742</v>
+        <v>73.56339054060091</v>
       </c>
     </row>
     <row r="913" spans="1:4">
@@ -14363,7 +14363,7 @@
         <v>118</v>
       </c>
       <c r="D913">
-        <v>-0.0688990060224826</v>
+        <v>73.512706095722</v>
       </c>
     </row>
     <row r="914" spans="1:4">
@@ -14377,7 +14377,7 @@
         <v>119</v>
       </c>
       <c r="D914">
-        <v>0.600218228527827</v>
+        <v>73.95394275799261</v>
       </c>
     </row>
     <row r="915" spans="1:4">
@@ -14391,7 +14391,7 @@
         <v>120</v>
       </c>
       <c r="D915">
-        <v>-0.732784647150719</v>
+        <v>73.4120196194994</v>
       </c>
     </row>
     <row r="916" spans="1:4">
@@ -14405,7 +14405,7 @@
         <v>121</v>
       </c>
       <c r="D916">
-        <v>0.125454820641702</v>
+        <v>73.5041185370425</v>
       </c>
     </row>
     <row r="917" spans="1:4">
@@ -14419,7 +14419,7 @@
         <v>122</v>
       </c>
       <c r="D917">
-        <v>-0.290943270868882</v>
+        <v>73.29026325034749</v>
       </c>
     </row>
     <row r="918" spans="1:4">
@@ -14433,7 +14433,7 @@
         <v>123</v>
       </c>
       <c r="D918">
-        <v>0.82511026937202</v>
+        <v>73.8949887388759</v>
       </c>
     </row>
     <row r="919" spans="1:4">
@@ -14447,7 +14447,7 @@
         <v>124</v>
       </c>
       <c r="D919">
-        <v>0.0304788625566932</v>
+        <v>73.91751109092991</v>
       </c>
     </row>
     <row r="920" spans="1:4">
@@ -14461,7 +14461,7 @@
         <v>125</v>
       </c>
       <c r="D920">
-        <v>-0.9255983893269319</v>
+        <v>73.2333317988417</v>
       </c>
     </row>
     <row r="921" spans="1:4">
@@ -14475,7 +14475,7 @@
         <v>126</v>
       </c>
       <c r="D921">
-        <v>0.306598409473491</v>
+        <v>73.45786402934139</v>
       </c>
     </row>
     <row r="922" spans="1:4">
@@ -14489,7 +14489,7 @@
         <v>127</v>
       </c>
       <c r="D922">
-        <v>0.397071579818054</v>
+        <v>73.7495443305433</v>
       </c>
     </row>
     <row r="923" spans="1:4">
@@ -14503,7 +14503,7 @@
         <v>128</v>
       </c>
       <c r="D923">
-        <v>0.1854858294424</v>
+        <v>73.88633928455479</v>
       </c>
     </row>
     <row r="924" spans="1:4">
@@ -14517,7 +14517,7 @@
         <v>129</v>
       </c>
       <c r="D924">
-        <v>1.20845001526764</v>
+        <v>74.7792187629197</v>
       </c>
     </row>
     <row r="925" spans="1:4">
@@ -14531,7 +14531,7 @@
         <v>130</v>
       </c>
       <c r="D925">
-        <v>0.469265924567419</v>
+        <v>75.13013215523181</v>
       </c>
     </row>
     <row r="926" spans="1:4">
@@ -14545,7 +14545,7 @@
         <v>131</v>
       </c>
       <c r="D926">
-        <v>0.298635993325846</v>
+        <v>75.3544977716806</v>
       </c>
     </row>
     <row r="927" spans="1:4">
@@ -14559,7 +14559,7 @@
         <v>132</v>
       </c>
       <c r="D927">
-        <v>1.22950754167084</v>
+        <v>76.2809870047716</v>
       </c>
     </row>
     <row r="928" spans="1:4">
@@ -14573,7 +14573,7 @@
         <v>133</v>
       </c>
       <c r="D928">
-        <v>-0.340993000436451</v>
+        <v>76.02087417842149</v>
       </c>
     </row>
     <row r="929" spans="1:4">
@@ -14587,7 +14587,7 @@
         <v>134</v>
       </c>
       <c r="D929">
-        <v>0.166931279644822</v>
+        <v>76.14777679648471</v>
       </c>
     </row>
     <row r="930" spans="1:4">
@@ -14601,7 +14601,7 @@
         <v>135</v>
       </c>
       <c r="D930">
-        <v>0.470757081735118</v>
+        <v>76.50624784833801</v>
       </c>
     </row>
     <row r="931" spans="1:4">
@@ -14615,7 +14615,7 @@
         <v>136</v>
       </c>
       <c r="D931">
-        <v>-0.602405487237634</v>
+        <v>76.04537001321999</v>
       </c>
     </row>
     <row r="932" spans="1:4">
@@ -14629,7 +14629,7 @@
         <v>137</v>
       </c>
       <c r="D932">
-        <v>0.250312742589198</v>
+        <v>76.23572126451219</v>
       </c>
     </row>
     <row r="933" spans="1:4">
@@ -14643,7 +14643,7 @@
         <v>138</v>
       </c>
       <c r="D933">
-        <v>-0.0143458358501602</v>
+        <v>76.2247846130804</v>
       </c>
     </row>
     <row r="934" spans="1:4">
@@ -14657,7 +14657,7 @@
         <v>139</v>
       </c>
       <c r="D934">
-        <v>0.299716668434113</v>
+        <v>76.45324299804381</v>
       </c>
     </row>
     <row r="935" spans="1:4">
@@ -14671,7 +14671,7 @@
         <v>140</v>
       </c>
       <c r="D935">
-        <v>0.892949767491968</v>
+        <v>77.1359320536349</v>
       </c>
     </row>
     <row r="936" spans="1:4">
@@ -14685,7 +14685,7 @@
         <v>141</v>
       </c>
       <c r="D936">
-        <v>-0.0879711574043318</v>
+        <v>77.06807468143271</v>
       </c>
     </row>
     <row r="937" spans="1:4">
@@ -14699,7 +14699,7 @@
         <v>142</v>
       </c>
       <c r="D937">
-        <v>0.0860295867195937</v>
+        <v>77.13437602757389</v>
       </c>
     </row>
     <row r="938" spans="1:4">
@@ -14713,7 +14713,7 @@
         <v>143</v>
       </c>
       <c r="D938">
-        <v>0.178411087304853</v>
+        <v>77.27199230653051</v>
       </c>
     </row>
     <row r="939" spans="1:4">
@@ -14727,7 +14727,7 @@
         <v>144</v>
       </c>
       <c r="D939">
-        <v>-0.435536805186476</v>
+        <v>76.9354443399347</v>
       </c>
     </row>
     <row r="940" spans="1:4">
@@ -14741,7 +14741,7 @@
         <v>145</v>
       </c>
       <c r="D940">
-        <v>0.51543440881352</v>
+        <v>77.3319960926363</v>
       </c>
     </row>
     <row r="941" spans="1:4">
@@ -14755,7 +14755,7 @@
         <v>146</v>
       </c>
       <c r="D941">
-        <v>0.234062631258181</v>
+        <v>77.5130013974952</v>
       </c>
     </row>
     <row r="942" spans="1:4">
@@ -14769,7 +14769,7 @@
         <v>147</v>
       </c>
       <c r="D942">
-        <v>-0.840883981317309</v>
+        <v>76.8612069853054</v>
       </c>
     </row>
     <row r="943" spans="1:4">
@@ -14783,7 +14783,7 @@
         <v>148</v>
       </c>
       <c r="D943">
-        <v>0.32812594517897</v>
+        <v>77.1134085472019</v>
       </c>
     </row>
     <row r="944" spans="1:4">
@@ -14797,7 +14797,7 @@
         <v>149</v>
       </c>
       <c r="D944">
-        <v>1.3083630258572</v>
+        <v>78.1223318726117</v>
       </c>
     </row>
     <row r="945" spans="1:4">
@@ -14811,7 +14811,7 @@
         <v>150</v>
       </c>
       <c r="D945">
-        <v>0.529317674483898</v>
+        <v>78.5358471829324</v>
       </c>
     </row>
     <row r="946" spans="1:4">
@@ -14825,7 +14825,7 @@
         <v>151</v>
       </c>
       <c r="D946">
-        <v>0.284830019384597</v>
+        <v>78.7595408516874</v>
       </c>
     </row>
     <row r="947" spans="1:4">
@@ -14839,7 +14839,7 @@
         <v>152</v>
       </c>
       <c r="D947">
-        <v>0.911525854451201</v>
+        <v>79.4774544293976</v>
       </c>
     </row>
     <row r="948" spans="1:4">
@@ -14853,7 +14853,7 @@
         <v>153</v>
       </c>
       <c r="D948">
-        <v>0.616198357793718</v>
+        <v>79.9671931984078</v>
       </c>
     </row>
     <row r="949" spans="1:4">
@@ -14867,7 +14867,7 @@
         <v>154</v>
       </c>
       <c r="D949">
-        <v>1.86014889426058</v>
+        <v>81.4547020584592</v>
       </c>
     </row>
     <row r="950" spans="1:4">
@@ -14881,7 +14881,7 @@
         <v>155</v>
       </c>
       <c r="D950">
-        <v>-1.04805648583555</v>
+        <v>80.6010107705175</v>
       </c>
     </row>
     <row r="951" spans="1:4">
@@ -14895,7 +14895,7 @@
         <v>156</v>
       </c>
       <c r="D951">
-        <v>0.101828487623146</v>
+        <v>80.6830855607941</v>
       </c>
     </row>
     <row r="952" spans="1:4">
@@ -14909,7 +14909,7 @@
         <v>157</v>
       </c>
       <c r="D952">
-        <v>0.544531861750963</v>
+        <v>81.1224306687164</v>
       </c>
     </row>
     <row r="953" spans="1:4">
@@ -14923,7 +14923,7 @@
         <v>158</v>
       </c>
       <c r="D953">
-        <v>1.02665251227829</v>
+        <v>81.955276141198</v>
       </c>
     </row>
     <row r="954" spans="1:4">
@@ -14937,7 +14937,7 @@
         <v>159</v>
       </c>
       <c r="D954">
-        <v>-0.146184077310518</v>
+        <v>81.8354705769637</v>
       </c>
     </row>
     <row r="955" spans="1:4">
@@ -14951,7 +14951,7 @@
         <v>160</v>
       </c>
       <c r="D955">
-        <v>-0.0468065134788698</v>
+        <v>81.79716624639759</v>
       </c>
     </row>
     <row r="956" spans="1:4">
@@ -14965,7 +14965,7 @@
         <v>161</v>
       </c>
       <c r="D956">
-        <v>0.254417671761553</v>
+        <v>82.0052726923286</v>
       </c>
     </row>
     <row r="957" spans="1:4">
@@ -14979,7 +14979,7 @@
         <v>162</v>
       </c>
       <c r="D957">
-        <v>-0.036785074157708</v>
+        <v>81.9751069919555</v>
       </c>
     </row>
     <row r="958" spans="1:4">
@@ -14993,7 +14993,7 @@
         <v>163</v>
       </c>
       <c r="D958">
-        <v>0.285075229037424</v>
+        <v>82.2087977159665</v>
       </c>
     </row>
     <row r="959" spans="1:4">
@@ -15007,7 +15007,7 @@
         <v>164</v>
       </c>
       <c r="D959">
-        <v>-0.326998499714082</v>
+        <v>81.9399761808023</v>
       </c>
     </row>
     <row r="960" spans="1:4">
@@ -15021,7 +15021,7 @@
         <v>165</v>
       </c>
       <c r="D960">
-        <v>0.460270705516197</v>
+        <v>82.31712188726949</v>
       </c>
     </row>
     <row r="961" spans="1:4">
@@ -15035,7 +15035,7 @@
         <v>166</v>
       </c>
       <c r="D961">
-        <v>0.0887322661855539</v>
+        <v>82.3901637349788</v>
       </c>
     </row>
     <row r="962" spans="1:4">
@@ -15049,7 +15049,7 @@
         <v>167</v>
       </c>
       <c r="D962">
-        <v>0.0657334942389509</v>
+        <v>82.44432166851099</v>
       </c>
     </row>
     <row r="963" spans="1:4">
@@ -15063,7 +15063,7 @@
         <v>168</v>
       </c>
       <c r="D963">
-        <v>0.567817349531907</v>
+        <v>82.9124548306487</v>
       </c>
     </row>
     <row r="964" spans="1:4">
@@ -15077,7 +15077,7 @@
         <v>169</v>
       </c>
       <c r="D964">
-        <v>0.455760830752916</v>
+        <v>83.29033732358251</v>
       </c>
     </row>
     <row r="965" spans="1:4">
@@ -15091,7 +15091,7 @@
         <v>170</v>
       </c>
       <c r="D965">
-        <v>0.217287599396543</v>
+        <v>83.47131689808219</v>
       </c>
     </row>
     <row r="966" spans="1:4">
@@ -15105,7 +15105,7 @@
         <v>171</v>
       </c>
       <c r="D966">
-        <v>0.418336338873471</v>
+        <v>83.8205077492031</v>
       </c>
     </row>
     <row r="967" spans="1:4">
@@ -15119,7 +15119,7 @@
         <v>172</v>
       </c>
       <c r="D967">
-        <v>-0.17170109464969</v>
+        <v>83.6765870198568</v>
       </c>
     </row>
     <row r="968" spans="1:4">
@@ -15133,7 +15133,7 @@
         <v>173</v>
       </c>
       <c r="D968">
-        <v>0.231348331861647</v>
+        <v>83.87017140808599</v>
       </c>
     </row>
     <row r="969" spans="1:4">
@@ -15147,7 +15147,7 @@
         <v>174</v>
       </c>
       <c r="D969">
-        <v>0.204720340985665</v>
+        <v>84.0418707089779</v>
       </c>
     </row>
     <row r="970" spans="1:4">
@@ -15161,7 +15161,7 @@
         <v>175</v>
       </c>
       <c r="D970">
-        <v>-0.146338556433356</v>
+        <v>83.91888504858279</v>
       </c>
     </row>
     <row r="971" spans="1:4">
@@ -15175,7 +15175,7 @@
         <v>176</v>
       </c>
       <c r="D971">
-        <v>-0.380763791881411</v>
+        <v>83.59935231976721</v>
       </c>
     </row>
     <row r="972" spans="1:4">
@@ -15189,7 +15189,7 @@
         <v>177</v>
       </c>
       <c r="D972">
-        <v>0.0502093995884634</v>
+        <v>83.64132705262681</v>
       </c>
     </row>
     <row r="973" spans="1:4">
@@ -15203,7 +15203,7 @@
         <v>178</v>
       </c>
       <c r="D973">
-        <v>0.588761708775065</v>
+        <v>84.133775159024</v>
       </c>
     </row>
     <row r="974" spans="1:4">
@@ -15217,7 +15217,7 @@
         <v>179</v>
       </c>
       <c r="D974">
-        <v>0.140010264029233</v>
+        <v>84.2515710797619</v>
       </c>
     </row>
     <row r="975" spans="1:4">
@@ -15231,7 +15231,7 @@
         <v>180</v>
       </c>
       <c r="D975">
-        <v>-1.38024239977019</v>
+        <v>83.08869517324651</v>
       </c>
     </row>
     <row r="976" spans="1:4">
@@ -15245,7 +15245,7 @@
         <v>181</v>
       </c>
       <c r="D976">
-        <v>1.92613250506852</v>
+        <v>84.6890935390157</v>
       </c>
     </row>
     <row r="977" spans="1:4">
@@ -15259,7 +15259,7 @@
         <v>182</v>
       </c>
       <c r="D977">
-        <v>-0.5256177119950191</v>
+        <v>84.2439526632466</v>
       </c>
     </row>
     <row r="978" spans="1:4">
@@ -15273,7 +15273,7 @@
         <v>183</v>
       </c>
       <c r="D978">
-        <v>0.798440963350644</v>
+        <v>84.91659089045569</v>
       </c>
     </row>
     <row r="979" spans="1:4">
@@ -15287,7 +15287,7 @@
         <v>184</v>
       </c>
       <c r="D979">
-        <v>-0.07841953875055151</v>
+        <v>84.8499996915567</v>
       </c>
     </row>
     <row r="980" spans="1:4">
@@ -15301,7 +15301,7 @@
         <v>185</v>
       </c>
       <c r="D980">
-        <v>-1.07946107072638</v>
+        <v>83.9340769763749</v>
       </c>
     </row>
     <row r="981" spans="1:4">
@@ -15315,7 +15315,7 @@
         <v>186</v>
       </c>
       <c r="D981">
-        <v>-0.293184792976353</v>
+        <v>83.6879950265551</v>
       </c>
     </row>
     <row r="982" spans="1:4">
@@ -15329,7 +15329,7 @@
         <v>187</v>
       </c>
       <c r="D982">
-        <v>0.101809335484093</v>
+        <v>83.7731972181716</v>
       </c>
     </row>
     <row r="983" spans="1:4">
@@ -15343,7 +15343,7 @@
         <v>188</v>
       </c>
       <c r="D983">
-        <v>-1.35499879361984</v>
+        <v>82.63807140648861</v>
       </c>
     </row>
     <row r="984" spans="1:4">
@@ -15357,7 +15357,7 @@
         <v>189</v>
       </c>
       <c r="D984">
-        <v>-1.12141270688347</v>
+        <v>81.7113575730128</v>
       </c>
     </row>
     <row r="985" spans="1:4">
@@ -15371,7 +15371,7 @@
         <v>190</v>
       </c>
       <c r="D985">
-        <v>-4.35151843326913</v>
+        <v>78.1556727861487</v>
       </c>
     </row>
     <row r="986" spans="1:4">
@@ -15385,7 +15385,7 @@
         <v>191</v>
       </c>
       <c r="D986">
-        <v>-0.386771061845903</v>
+        <v>77.8533892606209</v>
       </c>
     </row>
     <row r="987" spans="1:4">
@@ -15399,7 +15399,7 @@
         <v>192</v>
       </c>
       <c r="D987">
-        <v>-0.244403007911242</v>
+        <v>77.6631132355071</v>
       </c>
     </row>
     <row r="988" spans="1:4">
@@ -15413,7 +15413,7 @@
         <v>193</v>
       </c>
       <c r="D988">
-        <v>-0.869779051318886</v>
+        <v>76.98761574598259</v>
       </c>
     </row>
     <row r="989" spans="1:4">
@@ -15427,7 +15427,7 @@
         <v>194</v>
       </c>
       <c r="D989">
-        <v>-0.467658568850249</v>
+        <v>76.627576563993</v>
       </c>
     </row>
     <row r="990" spans="1:4">
@@ -15441,7 +15441,7 @@
         <v>195</v>
       </c>
       <c r="D990">
-        <v>1.58583577383644</v>
+        <v>77.84276408576871</v>
       </c>
     </row>
     <row r="991" spans="1:4">
@@ -15455,7 +15455,7 @@
         <v>196</v>
       </c>
       <c r="D991">
-        <v>1.7849667621618</v>
+        <v>79.2322315514477</v>
       </c>
     </row>
     <row r="992" spans="1:4">
@@ -15469,7 +15469,7 @@
         <v>197</v>
       </c>
       <c r="D992">
-        <v>-0.196659511523434</v>
+        <v>79.07641383190951</v>
       </c>
     </row>
     <row r="993" spans="1:4">
@@ -15483,7 +15483,7 @@
         <v>198</v>
       </c>
       <c r="D993">
-        <v>0.754510358712102</v>
+        <v>79.6730535655693</v>
       </c>
     </row>
     <row r="994" spans="1:4">
@@ -15497,7 +15497,7 @@
         <v>199</v>
       </c>
       <c r="D994">
-        <v>0.772650877370951</v>
+        <v>80.2886481129719</v>
       </c>
     </row>
     <row r="995" spans="1:4">
@@ -15511,7 +15511,7 @@
         <v>200</v>
       </c>
       <c r="D995">
-        <v>0.994767112109907</v>
+        <v>81.0873331791574</v>
       </c>
     </row>
     <row r="996" spans="1:4">
@@ -15525,7 +15525,7 @@
         <v>201</v>
       </c>
       <c r="D996">
-        <v>0.576211780630742</v>
+        <v>81.554567945535</v>
       </c>
     </row>
     <row r="997" spans="1:4">
@@ -15539,7 +15539,7 @@
         <v>202</v>
       </c>
       <c r="D997">
-        <v>-0.860239327838175</v>
+        <v>80.853003478419</v>
       </c>
     </row>
     <row r="998" spans="1:4">
@@ -15553,7 +15553,7 @@
         <v>203</v>
       </c>
       <c r="D998">
-        <v>0.8169937666900881</v>
+        <v>81.51356747701939</v>
       </c>
     </row>
     <row r="999" spans="1:4">
@@ -15567,7 +15567,7 @@
         <v>204</v>
       </c>
       <c r="D999">
-        <v>0.683370734365596</v>
+        <v>82.0706073416947</v>
       </c>
     </row>
     <row r="1000" spans="1:4">
@@ -15581,7 +15581,7 @@
         <v>205</v>
       </c>
       <c r="D1000">
-        <v>1.15424957990928</v>
+        <v>83.0179069821652</v>
       </c>
     </row>
     <row r="1001" spans="1:4">
@@ -15595,7 +15595,7 @@
         <v>206</v>
       </c>
       <c r="D1001">
-        <v>-0.19851274099828</v>
+        <v>82.8531058594955</v>
       </c>
     </row>
     <row r="1002" spans="1:4">
@@ -15609,7 +15609,7 @@
         <v>207</v>
       </c>
       <c r="D1002">
-        <v>-0.0280204065333023</v>
+        <v>82.8298900824082</v>
       </c>
     </row>
     <row r="1003" spans="1:4">
@@ -15623,7 +15623,7 @@
         <v>208</v>
       </c>
       <c r="D1003">
-        <v>0.346715038704715</v>
+        <v>83.1170737678665</v>
       </c>
     </row>
     <row r="1004" spans="1:4">
@@ -15637,7 +15637,7 @@
         <v>209</v>
       </c>
       <c r="D1004">
-        <v>0.229235069713862</v>
+        <v>83.3076072498624</v>
       </c>
     </row>
     <row r="1005" spans="1:4">
@@ -15651,7 +15651,7 @@
         <v>210</v>
       </c>
       <c r="D1005">
-        <v>0.289634649307979</v>
+        <v>83.5488949459674</v>
       </c>
     </row>
     <row r="1006" spans="1:4">
@@ -15665,7 +15665,7 @@
         <v>211</v>
       </c>
       <c r="D1006">
-        <v>-0.0404035925294255</v>
+        <v>83.5151381908906</v>
       </c>
     </row>
     <row r="1007" spans="1:4">
@@ -15679,7 +15679,7 @@
         <v>212</v>
       </c>
       <c r="D1007">
-        <v>0.200520998794662</v>
+        <v>83.68260358013571</v>
       </c>
     </row>
     <row r="1008" spans="1:4">
@@ -15693,7 +15693,7 @@
         <v>213</v>
       </c>
       <c r="D1008">
-        <v>0.814642199402615</v>
+        <v>84.3643173824583</v>
       </c>
     </row>
     <row r="1009" spans="1:4">
@@ -15707,7 +15707,7 @@
         <v>214</v>
       </c>
       <c r="D1009">
-        <v>0.140127986486127</v>
+        <v>84.4825354017191</v>
       </c>
     </row>
     <row r="1010" spans="1:4">
@@ -15721,7 +15721,7 @@
         <v>215</v>
       </c>
       <c r="D1010">
-        <v>0.225543706436415</v>
+        <v>84.6730804433556</v>
       </c>
     </row>
     <row r="1011" spans="1:4">
@@ -15735,7 +15735,7 @@
         <v>216</v>
       </c>
       <c r="D1011">
-        <v>0.631064297037298</v>
+        <v>85.2074220232353</v>
       </c>
     </row>
     <row r="1012" spans="1:4">
@@ -15749,7 +15749,7 @@
         <v>217</v>
       </c>
       <c r="D1012">
-        <v>-0.981557964363622</v>
+        <v>84.3710617861373</v>
       </c>
     </row>
     <row r="1013" spans="1:4">
@@ -15763,7 +15763,7 @@
         <v>218</v>
       </c>
       <c r="D1013">
-        <v>1.36932795937448</v>
+        <v>85.526378324796</v>
       </c>
     </row>
     <row r="1014" spans="1:4">
@@ -15777,7 +15777,7 @@
         <v>219</v>
       </c>
       <c r="D1014">
-        <v>0.40161604868707</v>
+        <v>85.8698659860092</v>
       </c>
     </row>
     <row r="1015" spans="1:4">
@@ -15791,7 +15791,7 @@
         <v>220</v>
       </c>
       <c r="D1015">
-        <v>0.303287513654471</v>
+        <v>86.1302985675366</v>
       </c>
     </row>
     <row r="1016" spans="1:4">
@@ -15805,7 +15805,7 @@
         <v>221</v>
       </c>
       <c r="D1016">
-        <v>0.826320664735558</v>
+        <v>86.84201102319859</v>
       </c>
     </row>
     <row r="1017" spans="1:4">
@@ -15819,7 +15819,7 @@
         <v>222</v>
       </c>
       <c r="D1017">
-        <v>0.120213325318219</v>
+        <v>86.9464066924228</v>
       </c>
     </row>
     <row r="1018" spans="1:4">
@@ -15833,7 +15833,7 @@
         <v>223</v>
       </c>
       <c r="D1018">
-        <v>0.0473501506260465</v>
+        <v>86.9875759469556</v>
       </c>
     </row>
     <row r="1019" spans="1:4">
@@ -15847,7 +15847,7 @@
         <v>224</v>
       </c>
       <c r="D1019">
-        <v>0.705222892720658</v>
+        <v>87.6010322463563</v>
       </c>
     </row>
     <row r="1020" spans="1:4">
@@ -15861,7 +15861,7 @@
         <v>225</v>
       </c>
       <c r="D1020">
-        <v>-0.0546249660210885</v>
+        <v>87.5531802122576</v>
       </c>
     </row>
     <row r="1021" spans="1:4">
@@ -15875,7 +15875,7 @@
         <v>226</v>
       </c>
       <c r="D1021">
-        <v>0.894545583631512</v>
+        <v>88.3363833191753</v>
       </c>
     </row>
     <row r="1022" spans="1:4">
@@ -15889,7 +15889,7 @@
         <v>227</v>
       </c>
       <c r="D1022">
-        <v>0.20546748393977</v>
+        <v>88.51788586338461</v>
       </c>
     </row>
     <row r="1023" spans="1:4">
@@ -15903,7 +15903,7 @@
         <v>228</v>
       </c>
       <c r="D1023">
-        <v>0.196228727209524</v>
+        <v>88.6915833841671</v>
       </c>
     </row>
     <row r="1024" spans="1:4">
@@ -15917,7 +15917,7 @@
         <v>229</v>
       </c>
       <c r="D1024">
-        <v>0.244924542556069</v>
+        <v>88.9088108390565</v>
       </c>
     </row>
     <row r="1025" spans="1:4">
@@ -15931,7 +15931,7 @@
         <v>230</v>
       </c>
       <c r="D1025">
-        <v>-0.443833386109749</v>
+        <v>88.5142038533596</v>
       </c>
     </row>
     <row r="1026" spans="1:4">
@@ -15945,7 +15945,7 @@
         <v>231</v>
       </c>
       <c r="D1026">
-        <v>0.67545609028592</v>
+        <v>89.11207843405521</v>
       </c>
     </row>
     <row r="1027" spans="1:4">
@@ -15959,7 +15959,7 @@
         <v>232</v>
       </c>
       <c r="D1027">
-        <v>0.404107447885727</v>
+        <v>89.472186979973</v>
       </c>
     </row>
     <row r="1028" spans="1:4">
@@ -15973,7 +15973,7 @@
         <v>233</v>
       </c>
       <c r="D1028">
-        <v>-0.572745819509257</v>
+        <v>88.9597387694217</v>
       </c>
     </row>
     <row r="1029" spans="1:4">
@@ -15987,7 +15987,7 @@
         <v>234</v>
       </c>
       <c r="D1029">
-        <v>0.399649989195328</v>
+        <v>89.3152663558019</v>
       </c>
     </row>
     <row r="1030" spans="1:4">
@@ -16001,7 +16001,7 @@
         <v>235</v>
       </c>
       <c r="D1030">
-        <v>-0.112050167662614</v>
+        <v>89.21518845010191</v>
       </c>
     </row>
     <row r="1031" spans="1:4">
@@ -16015,7 +16015,7 @@
         <v>236</v>
       </c>
       <c r="D1031">
-        <v>0.974239553041945</v>
+        <v>90.0843581033037</v>
       </c>
     </row>
     <row r="1032" spans="1:4">
@@ -16029,7 +16029,7 @@
         <v>237</v>
       </c>
       <c r="D1032">
-        <v>-0.357178349405141</v>
+        <v>89.7625962799581</v>
       </c>
     </row>
     <row r="1033" spans="1:4">
@@ -16043,7 +16043,7 @@
         <v>238</v>
       </c>
       <c r="D1033">
-        <v>-0.0870590644980629</v>
+        <v>89.6844498033676</v>
       </c>
     </row>
     <row r="1034" spans="1:4">
@@ -16057,7 +16057,7 @@
         <v>239</v>
       </c>
       <c r="D1034">
-        <v>-0.139959318950611</v>
+        <v>89.5589280582182</v>
       </c>
     </row>
     <row r="1035" spans="1:4">
@@ -16071,7 +16071,7 @@
         <v>240</v>
       </c>
       <c r="D1035">
-        <v>-0.0690991315545619</v>
+        <v>89.4970436167004</v>
       </c>
     </row>
     <row r="1036" spans="1:4">
@@ -16085,7 +16085,7 @@
         <v>241</v>
       </c>
       <c r="D1036">
-        <v>-0.335437896452007</v>
+        <v>89.1968366162058</v>
       </c>
     </row>
     <row r="1037" spans="1:4">
@@ -16099,7 +16099,7 @@
         <v>242</v>
       </c>
       <c r="D1037">
-        <v>0.818326784524204</v>
+        <v>89.9267582211845</v>
       </c>
     </row>
     <row r="1038" spans="1:4">
@@ -16113,7 +16113,7 @@
         <v>243</v>
       </c>
       <c r="D1038">
-        <v>-0.316599749079383</v>
+        <v>89.642050330301</v>
       </c>
     </row>
     <row r="1039" spans="1:4">
@@ -16127,7 +16127,7 @@
         <v>244</v>
       </c>
       <c r="D1039">
-        <v>0.0550659100655437</v>
+        <v>89.6914125411168</v>
       </c>
     </row>
     <row r="1040" spans="1:4">
@@ -16141,7 +16141,7 @@
         <v>245</v>
       </c>
       <c r="D1040">
-        <v>0.630737155343786</v>
+        <v>90.2571296051663</v>
       </c>
     </row>
     <row r="1041" spans="1:4">
@@ -16155,7 +16155,7 @@
         <v>246</v>
       </c>
       <c r="D1041">
-        <v>-0.13687408132369</v>
+        <v>90.13359098819009</v>
       </c>
     </row>
     <row r="1042" spans="1:4">
@@ -16169,7 +16169,7 @@
         <v>247</v>
       </c>
       <c r="D1042">
-        <v>0.317327436550796</v>
+        <v>90.4196096019441</v>
       </c>
     </row>
     <row r="1043" spans="1:4">
@@ -16183,7 +16183,7 @@
         <v>248</v>
       </c>
       <c r="D1043">
-        <v>-0.227972798821041</v>
+        <v>90.2134774872515</v>
       </c>
     </row>
     <row r="1044" spans="1:4">
@@ -16197,7 +16197,7 @@
         <v>249</v>
       </c>
       <c r="D1044">
-        <v>0.599471169391541</v>
+        <v>90.7542812756931</v>
       </c>
     </row>
     <row r="1045" spans="1:4">
@@ -16211,7 +16211,7 @@
         <v>250</v>
       </c>
       <c r="D1045">
-        <v>-0.814324063360461</v>
+        <v>90.0152473247353</v>
       </c>
     </row>
     <row r="1046" spans="1:4">
@@ -16225,7 +16225,7 @@
         <v>251</v>
       </c>
       <c r="D1046">
-        <v>1.3124604486813</v>
+        <v>91.19666184365509</v>
       </c>
     </row>
     <row r="1047" spans="1:4">
@@ -16239,7 +16239,7 @@
         <v>252</v>
       </c>
       <c r="D1047">
-        <v>0.281098475702413</v>
+        <v>91.4530142699891</v>
       </c>
     </row>
     <row r="1048" spans="1:4">
@@ -16253,7 +16253,7 @@
         <v>253</v>
       </c>
       <c r="D1048">
-        <v>0.457899871940048</v>
+        <v>91.8717775052167</v>
       </c>
     </row>
     <row r="1049" spans="1:4">
@@ -16267,7 +16267,7 @@
         <v>254</v>
       </c>
       <c r="D1049">
-        <v>0.736474479838356</v>
+        <v>92.5483897007165</v>
       </c>
     </row>
     <row r="1050" spans="1:4">
@@ -16281,7 +16281,7 @@
         <v>255</v>
       </c>
       <c r="D1050">
-        <v>-0.369085450739459</v>
+        <v>92.20680705943749</v>
       </c>
     </row>
     <row r="1051" spans="1:4">
@@ -16295,7 +16295,7 @@
         <v>256</v>
       </c>
       <c r="D1051">
-        <v>0.615325115394327</v>
+        <v>92.77417870137739</v>
       </c>
     </row>
     <row r="1052" spans="1:4">
@@ -16309,7 +16309,7 @@
         <v>257</v>
       </c>
       <c r="D1052">
-        <v>-0.674051381866458</v>
+        <v>92.14883306782551</v>
       </c>
     </row>
     <row r="1053" spans="1:4">
@@ -16323,7 +16323,7 @@
         <v>258</v>
       </c>
       <c r="D1053">
-        <v>0.228516240551846</v>
+        <v>92.3594081168645</v>
       </c>
     </row>
     <row r="1054" spans="1:4">
@@ -16337,7 +16337,7 @@
         <v>259</v>
       </c>
       <c r="D1054">
-        <v>0.704349559636364</v>
+        <v>93.0099412012184</v>
       </c>
     </row>
     <row r="1055" spans="1:4">
@@ -16351,7 +16351,7 @@
         <v>260</v>
       </c>
       <c r="D1055">
-        <v>0.157471192311731</v>
+        <v>93.1564050645964</v>
       </c>
     </row>
     <row r="1056" spans="1:4">
@@ -16365,7 +16365,7 @@
         <v>261</v>
       </c>
       <c r="D1056">
-        <v>-0.112778059977359</v>
+        <v>93.0513450782199</v>
       </c>
     </row>
     <row r="1057" spans="1:4">
@@ -16379,7 +16379,7 @@
         <v>262</v>
       </c>
       <c r="D1057">
-        <v>0.0712235233494951</v>
+        <v>93.1176195247087</v>
       </c>
     </row>
     <row r="1058" spans="1:4">
@@ -16393,7 +16393,7 @@
         <v>263</v>
       </c>
       <c r="D1058">
-        <v>0.380070428711932</v>
+        <v>93.4715320604426</v>
       </c>
     </row>
     <row r="1059" spans="1:4">
@@ -16407,7 +16407,7 @@
         <v>264</v>
       </c>
       <c r="D1059">
-        <v>0.210356662235345</v>
+        <v>93.6681556554252</v>
       </c>
     </row>
     <row r="1060" spans="1:4">
@@ -16421,7 +16421,7 @@
         <v>265</v>
       </c>
       <c r="D1060">
-        <v>0.899815380768088</v>
+        <v>94.5109961268945</v>
       </c>
     </row>
     <row r="1061" spans="1:4">
@@ -16435,7 +16435,7 @@
         <v>266</v>
       </c>
       <c r="D1061">
-        <v>-0.699952048570518</v>
+        <v>93.8494644733799</v>
       </c>
     </row>
     <row r="1062" spans="1:4">
@@ -16449,7 +16449,7 @@
         <v>267</v>
       </c>
       <c r="D1062">
-        <v>0.474933972681679</v>
+        <v>94.29518746334379</v>
       </c>
     </row>
     <row r="1063" spans="1:4">
@@ -16463,7 +16463,7 @@
         <v>268</v>
       </c>
       <c r="D1063">
-        <v>0.769814037456573</v>
+        <v>95.0210850530826</v>
       </c>
     </row>
     <row r="1064" spans="1:4">
@@ -16477,7 +16477,7 @@
         <v>269</v>
       </c>
       <c r="D1064">
-        <v>-0.0455187933596335</v>
+        <v>94.9778326017292</v>
       </c>
     </row>
     <row r="1065" spans="1:4">
@@ -16491,7 +16491,7 @@
         <v>270</v>
       </c>
       <c r="D1065">
-        <v>1.52971810501259</v>
+        <v>96.4307257027864</v>
       </c>
     </row>
     <row r="1066" spans="1:4">
@@ -16505,7 +16505,7 @@
         <v>271</v>
       </c>
       <c r="D1066">
-        <v>-1.23660674069079</v>
+        <v>95.2382568486487</v>
       </c>
     </row>
     <row r="1067" spans="1:4">
@@ -16519,7 +16519,7 @@
         <v>272</v>
       </c>
       <c r="D1067">
-        <v>-0.655740681079109</v>
+        <v>94.6137408545415</v>
       </c>
     </row>
     <row r="1068" spans="1:4">
@@ -16533,7 +16533,7 @@
         <v>273</v>
       </c>
       <c r="D1068">
-        <v>0.293929936020665</v>
+        <v>94.89183896250201</v>
       </c>
     </row>
     <row r="1069" spans="1:4">
@@ -16547,7 +16547,7 @@
         <v>274</v>
       </c>
       <c r="D1069">
-        <v>0.174309327542344</v>
+        <v>95.0572442888901</v>
       </c>
     </row>
     <row r="1070" spans="1:4">
@@ -16561,7 +16561,7 @@
         <v>275</v>
       </c>
       <c r="D1070">
-        <v>0.519283008854687</v>
+        <v>95.5508604071678</v>
       </c>
     </row>
     <row r="1071" spans="1:4">
@@ -16575,7 +16575,7 @@
         <v>276</v>
       </c>
       <c r="D1071">
-        <v>-0.476254609341931</v>
+        <v>95.0957950302128</v>
       </c>
     </row>
     <row r="1072" spans="1:4">
@@ -16589,7 +16589,7 @@
         <v>277</v>
       </c>
       <c r="D1072">
-        <v>0.09571475593792569</v>
+        <v>95.18681573833319</v>
       </c>
     </row>
     <row r="1073" spans="1:4">
@@ -16603,7 +16603,7 @@
         <v>278</v>
       </c>
       <c r="D1073">
-        <v>0.351944812502003</v>
+        <v>95.52182079851011</v>
       </c>
     </row>
     <row r="1074" spans="1:4">
@@ -16617,7 +16617,7 @@
         <v>279</v>
       </c>
       <c r="D1074">
-        <v>0.42281757424969</v>
+        <v>95.9257038440895</v>
       </c>
     </row>
     <row r="1075" spans="1:4">
@@ -16631,7 +16631,7 @@
         <v>280</v>
       </c>
       <c r="D1075">
-        <v>-0.09792146924234579</v>
+        <v>95.8317719855043</v>
       </c>
     </row>
     <row r="1076" spans="1:4">
@@ -16645,7 +16645,7 @@
         <v>281</v>
       </c>
       <c r="D1076">
-        <v>0.321474781878295</v>
+        <v>96.1398469654648</v>
       </c>
     </row>
     <row r="1077" spans="1:4">
@@ -16659,7 +16659,7 @@
         <v>282</v>
       </c>
       <c r="D1077">
-        <v>0.640181024426734</v>
+        <v>96.7553160226506</v>
       </c>
     </row>
     <row r="1078" spans="1:4">
@@ -16673,7 +16673,7 @@
         <v>283</v>
       </c>
       <c r="D1078">
-        <v>0.253260544759648</v>
+        <v>97.0003590630935</v>
       </c>
     </row>
     <row r="1079" spans="1:4">
@@ -16687,7 +16687,7 @@
         <v>284</v>
       </c>
       <c r="D1079">
-        <v>0.249431074226147</v>
+        <v>97.2423081007078</v>
       </c>
     </row>
     <row r="1080" spans="1:4">
@@ -16701,7 +16701,7 @@
         <v>285</v>
       </c>
       <c r="D1080">
-        <v>0.488593786335612</v>
+        <v>97.7174279757772</v>
       </c>
     </row>
     <row r="1081" spans="1:4">
@@ -16715,7 +16715,7 @@
         <v>286</v>
       </c>
       <c r="D1081">
-        <v>0.296002383113381</v>
+        <v>98.0066738913026</v>
       </c>
     </row>
     <row r="1082" spans="1:4">
@@ -16729,7 +16729,7 @@
         <v>287</v>
       </c>
       <c r="D1082">
-        <v>-0.469880364631536</v>
+        <v>97.5461597746589</v>
       </c>
     </row>
     <row r="1083" spans="1:4">
@@ -16743,7 +16743,7 @@
         <v>288</v>
       </c>
       <c r="D1083">
-        <v>0.335895730078462</v>
+        <v>97.8738131601975</v>
       </c>
     </row>
     <row r="1084" spans="1:4">
@@ -16757,7 +16757,7 @@
         <v>289</v>
       </c>
       <c r="D1084">
-        <v>-0.0256172209270766</v>
+        <v>97.8487406092505</v>
       </c>
     </row>
     <row r="1085" spans="1:4">
@@ -16771,7 +16771,7 @@
         <v>290</v>
       </c>
       <c r="D1085">
-        <v>-0.205127418374373</v>
+        <v>97.64802601372691</v>
       </c>
     </row>
     <row r="1086" spans="1:4">
@@ -16785,7 +16785,7 @@
         <v>291</v>
       </c>
       <c r="D1086">
-        <v>0.5198770785638021</v>
+        <v>98.1556757186423</v>
       </c>
     </row>
     <row r="1087" spans="1:4">
@@ -16799,7 +16799,7 @@
         <v>292</v>
       </c>
       <c r="D1087">
-        <v>-0.8778971811228</v>
+        <v>97.2939698083963</v>
       </c>
     </row>
     <row r="1088" spans="1:4">
@@ -16813,7 +16813,7 @@
         <v>293</v>
       </c>
       <c r="D1088">
-        <v>1.06767797941807</v>
+        <v>98.33275609934221</v>
       </c>
     </row>
     <row r="1089" spans="1:4">
@@ -16827,7 +16827,7 @@
         <v>294</v>
       </c>
       <c r="D1089">
-        <v>-1.19947444968797</v>
+        <v>97.15327981425661</v>
       </c>
     </row>
     <row r="1090" spans="1:4">
@@ -16841,7 +16841,7 @@
         <v>295</v>
       </c>
       <c r="D1090">
-        <v>1.35330138353935</v>
+        <v>98.4680564941368</v>
       </c>
     </row>
     <row r="1091" spans="1:4">
@@ -16855,7 +16855,7 @@
         <v>296</v>
       </c>
       <c r="D1091">
-        <v>0.743339693401657</v>
+        <v>99.20000864337889</v>
       </c>
     </row>
     <row r="1092" spans="1:4">
@@ -16869,7 +16869,7 @@
         <v>297</v>
       </c>
       <c r="D1092">
-        <v>0.63830758257053</v>
+        <v>99.8332098204602</v>
       </c>
     </row>
     <row r="1093" spans="1:4">
@@ -16883,7 +16883,7 @@
         <v>298</v>
       </c>
       <c r="D1093">
-        <v>-0.703093400986732</v>
+        <v>99.1312891102193</v>
       </c>
     </row>
     <row r="1094" spans="1:4">
@@ -16897,7 +16897,7 @@
         <v>299</v>
       </c>
       <c r="D1094">
-        <v>0.518941588932154</v>
+        <v>99.6457225970568</v>
       </c>
     </row>
     <row r="1095" spans="1:4">
@@ -16911,7 +16911,7 @@
         <v>300</v>
       </c>
       <c r="D1095">
-        <v>0.688239721296835</v>
+        <v>100.331524040543</v>
       </c>
     </row>
     <row r="1096" spans="1:4">
@@ -16925,7 +16925,7 @@
         <v>301</v>
       </c>
       <c r="D1096">
-        <v>-0.897187192827209</v>
+        <v>99.4313624564829</v>
       </c>
     </row>
     <row r="1097" spans="1:4">
@@ -16939,7 +16939,7 @@
         <v>302</v>
       </c>
       <c r="D1097">
-        <v>0.754917320277704</v>
+        <v>100.181987033455</v>
       </c>
     </row>
     <row r="1098" spans="1:4">
@@ -16953,7 +16953,7 @@
         <v>303</v>
       </c>
       <c r="D1098">
-        <v>-0.245678646881409</v>
+        <v>99.9358612832923</v>
       </c>
     </row>
     <row r="1099" spans="1:4">
@@ -16967,7 +16967,7 @@
         <v>304</v>
       </c>
       <c r="D1099">
-        <v>0.359646905011268</v>
+        <v>100.295277515394</v>
       </c>
     </row>
     <row r="1100" spans="1:4">
@@ -16981,7 +16981,7 @@
         <v>305</v>
       </c>
       <c r="D1100">
-        <v>0.285699397012995</v>
+        <v>100.581820518488</v>
       </c>
     </row>
     <row r="1101" spans="1:4">
@@ -16995,7 +16995,7 @@
         <v>306</v>
       </c>
       <c r="D1101">
-        <v>0.0974740212084102</v>
+        <v>100.679861663552</v>
       </c>
     </row>
     <row r="1102" spans="1:4">
@@ -17009,7 +17009,7 @@
         <v>307</v>
       </c>
       <c r="D1102">
-        <v>-0.115273232549551</v>
+        <v>100.563804732486</v>
       </c>
     </row>
     <row r="1103" spans="1:4">
@@ -17023,7 +17023,7 @@
         <v>308</v>
       </c>
       <c r="D1103">
-        <v>-0.514181887025378</v>
+        <v>100.046723863648</v>
       </c>
     </row>
     <row r="1104" spans="1:4">
@@ -17037,7 +17037,7 @@
         <v>309</v>
       </c>
       <c r="D1104">
-        <v>-0.399185863936824</v>
+        <v>99.6473514846524</v>
       </c>
     </row>
     <row r="1105" spans="1:4">
@@ -17051,7 +17051,7 @@
         <v>310</v>
       </c>
       <c r="D1105">
-        <v>0.503023074145426</v>
+        <v>100.148600655395</v>
       </c>
     </row>
     <row r="1106" spans="1:4">
@@ -17065,7 +17065,7 @@
         <v>311</v>
       </c>
       <c r="D1106">
-        <v>0.248129287632359</v>
+        <v>100.397098664775</v>
       </c>
     </row>
     <row r="1107" spans="1:4">
@@ -17079,7 +17079,7 @@
         <v>312</v>
       </c>
       <c r="D1107">
-        <v>-1.16626139195506</v>
+        <v>99.22620606440471</v>
       </c>
     </row>
     <row r="1108" spans="1:4">
@@ -17093,7 +17093,7 @@
         <v>313</v>
       </c>
       <c r="D1108">
-        <v>0.439419874816527</v>
+        <v>99.66222573487811</v>
       </c>
     </row>
     <row r="1109" spans="1:4">
@@ -17107,7 +17107,7 @@
         <v>314</v>
       </c>
       <c r="D1109">
-        <v>-0.417925931316065</v>
+        <v>99.2457114498053</v>
       </c>
     </row>
     <row r="1110" spans="1:4">
@@ -17121,7 +17121,7 @@
         <v>315</v>
       </c>
       <c r="D1110">
-        <v>0.504375787407274</v>
+        <v>99.7462827883982</v>
       </c>
     </row>
     <row r="1111" spans="1:4">
@@ -17135,7 +17135,7 @@
         <v>316</v>
       </c>
       <c r="D1111">
-        <v>-0.209490450096972</v>
+        <v>99.53732385162979</v>
       </c>
     </row>
     <row r="1112" spans="1:4">
@@ -17149,7 +17149,7 @@
         <v>317</v>
       </c>
       <c r="D1112">
-        <v>0.105968828252734</v>
+        <v>99.64280238738949</v>
       </c>
     </row>
     <row r="1113" spans="1:4">
@@ -17163,7 +17163,7 @@
         <v>318</v>
       </c>
       <c r="D1113">
-        <v>0.434034694726981</v>
+        <v>100.075286720549</v>
       </c>
     </row>
     <row r="1114" spans="1:4">
@@ -17177,7 +17177,7 @@
         <v>319</v>
       </c>
       <c r="D1114">
-        <v>-1.01482163011106</v>
+        <v>99.05970106451321</v>
       </c>
     </row>
     <row r="1115" spans="1:4">
@@ -17191,7 +17191,7 @@
         <v>320</v>
       </c>
       <c r="D1115">
-        <v>0.205156627383252</v>
+        <v>99.2629286063131</v>
       </c>
     </row>
     <row r="1116" spans="1:4">
@@ -17205,7 +17205,7 @@
         <v>321</v>
       </c>
       <c r="D1116">
-        <v>-0.175998025935109</v>
+        <v>99.08822781148061</v>
       </c>
     </row>
     <row r="1117" spans="1:4">
@@ -17219,7 +17219,7 @@
         <v>322</v>
       </c>
       <c r="D1117">
-        <v>0.840310917032894</v>
+        <v>99.9208770072749</v>
       </c>
     </row>
     <row r="1118" spans="1:4">
@@ -17233,7 +17233,7 @@
         <v>323</v>
       </c>
       <c r="D1118">
-        <v>-1.00806026547431</v>
+        <v>98.91361434925111</v>
       </c>
     </row>
     <row r="1119" spans="1:4">
@@ -17247,7 +17247,7 @@
         <v>324</v>
       </c>
       <c r="D1119">
-        <v>-3.28312447152468</v>
+        <v>95.6661572708813</v>
       </c>
     </row>
     <row r="1120" spans="1:4">
@@ -17261,7 +17261,7 @@
         <v>325</v>
       </c>
       <c r="D1120">
-        <v>-18.8715240184585</v>
+        <v>77.6124954239707</v>
       </c>
     </row>
     <row r="1121" spans="1:4">
@@ -17275,7 +17275,7 @@
         <v>326</v>
       </c>
       <c r="D1121">
-        <v>-1.86576952535115</v>
+        <v>76.1644251364857</v>
       </c>
     </row>
     <row r="1122" spans="1:4">
@@ -17289,7 +17289,7 @@
         <v>327</v>
       </c>
       <c r="D1122">
-        <v>11.8552153474137</v>
+        <v>85.19388175453579</v>
       </c>
     </row>
     <row r="1123" spans="1:4">
@@ -17303,7 +17303,7 @@
         <v>328</v>
       </c>
       <c r="D1123">
-        <v>5.06443190392565</v>
+        <v>89.5084678823052</v>
       </c>
     </row>
     <row r="1124" spans="1:4">
@@ -17317,7 +17317,7 @@
         <v>329</v>
       </c>
       <c r="D1124">
-        <v>2.93545649432239</v>
+        <v>92.1359500157248</v>
       </c>
     </row>
     <row r="1125" spans="1:4">
@@ -17331,7 +17331,7 @@
         <v>330</v>
       </c>
       <c r="D1125">
-        <v>2.71215495753072</v>
+        <v>94.6348197517443</v>
       </c>
     </row>
     <row r="1126" spans="1:4">
@@ -17345,7 +17345,7 @@
         <v>331</v>
       </c>
       <c r="D1126">
-        <v>1.06498486302344</v>
+        <v>95.6426662572499</v>
       </c>
     </row>
     <row r="1127" spans="1:4">
@@ -17359,7 +17359,7 @@
         <v>332</v>
       </c>
       <c r="D1127">
-        <v>0.77341981482455</v>
+        <v>96.38238558950999</v>
       </c>
     </row>
     <row r="1128" spans="1:4">
@@ -17373,7 +17373,7 @@
         <v>333</v>
       </c>
       <c r="D1128">
-        <v>-0.294144301304211</v>
+        <v>96.0988822948374</v>
       </c>
     </row>
     <row r="1129" spans="1:4">
@@ -17387,7 +17387,7 @@
         <v>334</v>
       </c>
       <c r="D1129">
-        <v>0.0539805083509259</v>
+        <v>96.15075696001971</v>
       </c>
     </row>
     <row r="1130" spans="1:4">
@@ -17401,7 +17401,7 @@
         <v>335</v>
       </c>
       <c r="D1130">
-        <v>-0.642745825691715</v>
+        <v>95.53275198328819</v>
       </c>
     </row>
     <row r="1131" spans="1:4">
@@ -17415,7 +17415,7 @@
         <v>336</v>
       </c>
       <c r="D1131">
-        <v>1.99021996249591</v>
+        <v>97.4340638839813</v>
       </c>
     </row>
     <row r="1132" spans="1:4">
@@ -17429,7 +17429,7 @@
         <v>337</v>
       </c>
       <c r="D1132">
-        <v>-0.189785396341657</v>
+        <v>97.24914825966729</v>
       </c>
     </row>
     <row r="1133" spans="1:4">
@@ -17443,7 +17443,7 @@
         <v>338</v>
       </c>
       <c r="D1133">
-        <v>0.00438704145264701</v>
+        <v>97.2534146201138</v>
       </c>
     </row>
     <row r="1134" spans="1:4">
@@ -17457,7 +17457,7 @@
         <v>339</v>
       </c>
       <c r="D1134">
-        <v>-0.167710625690121</v>
+        <v>97.0903103099494</v>
       </c>
     </row>
     <row r="1135" spans="1:4">
@@ -17471,7 +17471,7 @@
         <v>340</v>
       </c>
       <c r="D1135">
-        <v>-0.353138718993951</v>
+        <v>96.74744683185359</v>
       </c>
     </row>
     <row r="1136" spans="1:4">
@@ -17485,7 +17485,7 @@
         <v>341</v>
       </c>
       <c r="D1136">
-        <v>-0.745807330944082</v>
+        <v>96.0258972808804</v>
       </c>
     </row>
     <row r="1137" spans="1:4">
@@ -17499,7 +17499,7 @@
         <v>342</v>
       </c>
       <c r="D1137">
-        <v>-0.236336848444096</v>
+        <v>95.7989527015566</v>
       </c>
     </row>
     <row r="1138" spans="1:4">
@@ -17513,7 +17513,7 @@
         <v>343</v>
       </c>
       <c r="D1138">
-        <v>0.703696032203438</v>
+        <v>96.4730861306099</v>
       </c>
     </row>
     <row r="1139" spans="1:4">
@@ -17527,7 +17527,7 @@
         <v>344</v>
       </c>
       <c r="D1139">
-        <v>0.649428843904287</v>
+        <v>97.0996101785467</v>
       </c>
     </row>
     <row r="1140" spans="1:4">
@@ -17541,7 +17541,7 @@
         <v>345</v>
       </c>
       <c r="D1140">
-        <v>0.544029323702389</v>
+        <v>97.6278605311187</v>
       </c>
     </row>
     <row r="1141" spans="1:4">
@@ -17555,7 +17555,7 @@
         <v>346</v>
       </c>
       <c r="D1141">
-        <v>0.650823364370035</v>
+        <v>98.2632454575898</v>
       </c>
     </row>
     <row r="1142" spans="1:4">
@@ -17569,7 +17569,7 @@
         <v>347</v>
       </c>
       <c r="D1142">
-        <v>0.197573395421569</v>
+        <v>98.4573874880918</v>
       </c>
     </row>
     <row r="1143" spans="1:4">
@@ -17583,7 +17583,7 @@
         <v>348</v>
       </c>
       <c r="D1143">
-        <v>0.679671256307635</v>
+        <v>99.1265740505598</v>
       </c>
     </row>
     <row r="1144" spans="1:4">
@@ -17597,7 +17597,7 @@
         <v>349</v>
       </c>
       <c r="D1144">
-        <v>0.659553379836608</v>
+        <v>99.78036672002651</v>
       </c>
     </row>
     <row r="1145" spans="1:4">
@@ -17611,7 +17611,7 @@
         <v>350</v>
       </c>
       <c r="D1145">
-        <v>0.0262578366863497</v>
+        <v>99.80656688576489</v>
       </c>
     </row>
     <row r="1146" spans="1:4">
@@ -17625,7 +17625,7 @@
         <v>351</v>
       </c>
       <c r="D1146">
-        <v>-0.330555071608363</v>
+        <v>99.47665121712581</v>
       </c>
     </row>
     <row r="1147" spans="1:4">
@@ -17639,7 +17639,7 @@
         <v>352</v>
       </c>
       <c r="D1147">
-        <v>0.554926142829526</v>
+        <v>100.028673160741</v>
       </c>
     </row>
     <row r="1148" spans="1:4">
@@ -17653,7 +17653,7 @@
         <v>353</v>
       </c>
       <c r="D1148">
-        <v>0.492845649044837</v>
+        <v>100.521660124211</v>
       </c>
     </row>
     <row r="1149" spans="1:4">
@@ -17667,7 +17667,7 @@
         <v>354</v>
       </c>
       <c r="D1149">
-        <v>0.172300370840461</v>
+        <v>100.69485931738</v>
       </c>
     </row>
     <row r="1150" spans="1:4">
@@ -17681,7 +17681,7 @@
         <v>355</v>
       </c>
       <c r="D1150">
-        <v>0.39640801593841</v>
+        <v>101.094021811352</v>
       </c>
     </row>
     <row r="1151" spans="1:4">
@@ -17695,7 +17695,7 @@
         <v>356</v>
       </c>
       <c r="D1151">
-        <v>0.559252284660339</v>
+        <v>101.659392437987</v>
       </c>
     </row>
     <row r="1152" spans="1:4">
@@ -17709,7 +17709,7 @@
         <v>357</v>
       </c>
       <c r="D1152">
-        <v>0.861930771286601</v>
+        <v>102.535626023313</v>
       </c>
     </row>
     <row r="1153" spans="1:4">
@@ -17723,7 +17723,7 @@
         <v>358</v>
       </c>
       <c r="D1153">
-        <v>0.0608511633486408</v>
+        <v>102.598020144595</v>
       </c>
     </row>
     <row r="1154" spans="1:4">
@@ -17737,7 +17737,7 @@
         <v>359</v>
       </c>
       <c r="D1154">
-        <v>-0.649170817787048</v>
+        <v>101.931983738189</v>
       </c>
     </row>
     <row r="1155" spans="1:4">
@@ -17751,7 +17751,7 @@
         <v>360</v>
       </c>
       <c r="D1155">
-        <v>-0.208194499681358</v>
+        <v>101.71976695463</v>
       </c>
     </row>
     <row r="1156" spans="1:4">
@@ -17765,7 +17765,7 @@
         <v>361</v>
       </c>
       <c r="D1156">
-        <v>0.996971532158852</v>
+        <v>102.733884073746</v>
       </c>
     </row>
     <row r="1157" spans="1:4">
@@ -17779,7 +17779,7 @@
         <v>362</v>
       </c>
       <c r="D1157">
-        <v>0.17262885494107</v>
+        <v>102.911232401459</v>
       </c>
     </row>
     <row r="1158" spans="1:4">
@@ -17793,7 +17793,7 @@
         <v>363</v>
       </c>
       <c r="D1158">
-        <v>0.429127295928433</v>
+        <v>103.35285259027</v>
       </c>
     </row>
     <row r="1159" spans="1:4">
@@ -17807,7 +17807,7 @@
         <v>364</v>
       </c>
       <c r="D1159">
-        <v>0.0214137020598137</v>
+        <v>103.374984262194</v>
       </c>
     </row>
     <row r="1160" spans="1:4">
@@ -17821,7 +17821,7 @@
         <v>365</v>
       </c>
       <c r="D1160">
-        <v>0.333308097553942</v>
+        <v>103.719541455585</v>
       </c>
     </row>
     <row r="1161" spans="1:4">
@@ -17835,7 +17835,7 @@
         <v>366</v>
       </c>
       <c r="D1161">
-        <v>0.839259449457508</v>
+        <v>104.590017508185</v>
       </c>
     </row>
     <row r="1162" spans="1:4">
@@ -17849,7 +17849,7 @@
         <v>367</v>
       </c>
       <c r="D1162">
-        <v>0.028556904948096</v>
+        <v>104.61988518007</v>
       </c>
     </row>
     <row r="1163" spans="1:4">
@@ -17863,7 +17863,7 @@
         <v>368</v>
       </c>
       <c r="D1163">
-        <v>-0.734989349571069</v>
+        <v>103.850940166463</v>
       </c>
     </row>
     <row r="1164" spans="1:4">
@@ -17877,7 +17877,7 @@
         <v>369</v>
       </c>
       <c r="D1164">
-        <v>0.422643385143595</v>
+        <v>104.289859295486</v>
       </c>
     </row>
     <row r="1165" spans="1:4">
@@ -17891,7 +17891,7 @@
         <v>370</v>
       </c>
       <c r="D1165">
-        <v>0.0317834279937923</v>
+        <v>104.32300618782</v>
       </c>
     </row>
     <row r="1166" spans="1:4">
@@ -17905,7 +17905,7 @@
         <v>371</v>
       </c>
       <c r="D1166">
-        <v>0.335327522274609</v>
+        <v>104.672829939632</v>
       </c>
     </row>
     <row r="1167" spans="1:4">
@@ -17919,7 +17919,7 @@
         <v>372</v>
       </c>
       <c r="D1167">
-        <v>0.258301600458255</v>
+        <v>104.943201534611</v>
       </c>
     </row>
     <row r="1168" spans="1:4">
@@ -17933,7 +17933,7 @@
         <v>373</v>
       </c>
       <c r="D1168">
-        <v>-1.29286934111642</v>
+        <v>103.586423056384</v>
       </c>
     </row>
     <row r="1169" spans="1:4">
@@ -17947,7 +17947,7 @@
         <v>374</v>
       </c>
       <c r="D1169">
-        <v>0.81626037315794</v>
+        <v>104.431957979765</v>
       </c>
     </row>
     <row r="1170" spans="1:4">
@@ -17961,7 +17961,7 @@
         <v>375</v>
       </c>
       <c r="D1170">
-        <v>0.15077136242001</v>
+        <v>104.589411465613</v>
       </c>
     </row>
     <row r="1171" spans="1:4">
@@ -17975,7 +17975,7 @@
         <v>376</v>
       </c>
       <c r="D1171">
-        <v>1.00418971096161</v>
+        <v>105.639687574306</v>
       </c>
     </row>
     <row r="1172" spans="1:4">
@@ -17989,7 +17989,7 @@
         <v>377</v>
       </c>
       <c r="D1172">
-        <v>-0.8311450163097091</v>
+        <v>104.761668575787</v>
       </c>
     </row>
     <row r="1173" spans="1:4">
@@ -18003,7 +18003,7 @@
         <v>378</v>
       </c>
       <c r="D1173">
-        <v>0.24652045448299</v>
+        <v>105.019927517284</v>
       </c>
     </row>
     <row r="1174" spans="1:4">
@@ -18017,7 +18017,7 @@
         <v>379</v>
       </c>
       <c r="D1174">
-        <v>-0.957568238433126</v>
+        <v>104.014290047353</v>
       </c>
     </row>
     <row r="1175" spans="1:4">
@@ -18031,7 +18031,7 @@
         <v>380</v>
       </c>
       <c r="D1175">
-        <v>0.47154692022866</v>
+        <v>104.504766228669</v>
       </c>
     </row>
     <row r="1176" spans="1:4">
@@ -18045,7 +18045,7 @@
         <v>381</v>
       </c>
       <c r="D1176">
-        <v>-0.929280372056929</v>
+        <v>103.533623948242</v>
       </c>
     </row>
     <row r="1177" spans="1:4">
@@ -18059,7 +18059,7 @@
         <v>382</v>
       </c>
       <c r="D1177">
-        <v>0.73491051533594</v>
+        <v>104.294503437546</v>
       </c>
     </row>
     <row r="1178" spans="1:4">
@@ -18073,7 +18073,7 @@
         <v>383</v>
       </c>
       <c r="D1178">
-        <v>0.948250835299502</v>
+        <v>105.283476937564</v>
       </c>
     </row>
     <row r="1179" spans="1:4">
@@ -18087,7 +18087,7 @@
         <v>384</v>
       </c>
       <c r="D1179">
-        <v>-0.292047383306249</v>
+        <v>104.975999298114</v>
       </c>
     </row>
     <row r="1180" spans="1:4">
@@ -18101,7 +18101,7 @@
         <v>385</v>
       </c>
       <c r="D1180">
-        <v>-0.282126271786132</v>
+        <v>104.679834425024</v>
       </c>
     </row>
     <row r="1181" spans="1:4">
@@ -18115,7 +18115,7 @@
         <v>386</v>
       </c>
       <c r="D1181">
-        <v>0.189066664917936</v>
+        <v>104.877749096813</v>
       </c>
     </row>
     <row r="1182" spans="1:4">
@@ -18129,7 +18129,7 @@
         <v>387</v>
       </c>
       <c r="D1182">
-        <v>0.166639346313269</v>
+        <v>105.052516692336</v>
       </c>
     </row>
     <row r="1183" spans="1:4">
@@ -18143,7 +18143,7 @@
         <v>388</v>
       </c>
       <c r="D1183">
-        <v>-0.550297392419519</v>
+        <v>104.474415432307</v>
       </c>
     </row>
     <row r="1184" spans="1:4">
@@ -18157,7 +18157,7 @@
         <v>389</v>
       </c>
       <c r="D1184">
-        <v>0.474921123856875</v>
+        <v>104.970586500221</v>
       </c>
     </row>
     <row r="1185" spans="1:4">
@@ -18171,7 +18171,7 @@
         <v>390</v>
       </c>
       <c r="D1185">
-        <v>-0.437056003877845</v>
+        <v>104.511806249616</v>
       </c>
     </row>
     <row r="1186" spans="1:4">
@@ -18185,7 +18185,7 @@
         <v>391</v>
       </c>
       <c r="D1186">
-        <v>0.978663246992495</v>
+        <v>105.534624886149</v>
       </c>
     </row>
     <row r="1187" spans="1:4">
@@ -18199,7 +18199,7 @@
         <v>392</v>
       </c>
       <c r="D1187">
-        <v>-0.0862251333182518</v>
+        <v>105.443627515144</v>
       </c>
     </row>
     <row r="1188" spans="1:4">
@@ -18213,7 +18213,7 @@
         <v>393</v>
       </c>
       <c r="D1188">
-        <v>0.393671729628586</v>
+        <v>105.858729267366</v>
       </c>
     </row>
     <row r="1189" spans="1:4">
@@ -18227,7 +18227,7 @@
         <v>394</v>
       </c>
       <c r="D1189">
-        <v>-1.00989027495494</v>
+        <v>104.789672255304</v>
       </c>
     </row>
     <row r="1190" spans="1:4">
@@ -18241,7 +18241,7 @@
         <v>395</v>
       </c>
       <c r="D1190">
-        <v>0.280673190736236</v>
+        <v>105.083788771985</v>
       </c>
     </row>
     <row r="1191" spans="1:4">
@@ -18255,7 +18255,7 @@
         <v>396</v>
       </c>
       <c r="D1191">
-        <v>0.485302413528843</v>
+        <v>105.593762935123</v>
       </c>
     </row>
     <row r="1192" spans="1:4">
@@ -18269,7 +18269,7 @@
         <v>397</v>
       </c>
       <c r="D1192">
-        <v>1.64421504467336</v>
+        <v>107.329951471539</v>
       </c>
     </row>
     <row r="1193" spans="1:4">
@@ -18283,7 +18283,7 @@
         <v>398</v>
       </c>
       <c r="D1193">
-        <v>-0.443561089393807</v>
+        <v>106.853877569546</v>
       </c>
     </row>
     <row r="1194" spans="1:4">
@@ -18297,7 +18297,7 @@
         <v>399</v>
       </c>
       <c r="D1194">
-        <v>-0.0584933562905232</v>
+        <v>106.791375150229</v>
       </c>
     </row>
   </sheetData>
